--- a/p/ds_25/databricks/topic-list_DtBrk.xlsx
+++ b/p/ds_25/databricks/topic-list_DtBrk.xlsx
@@ -4,15 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15650" windowHeight="17600" tabRatio="698"/>
+    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="what" sheetId="21" r:id="rId1"/>
-    <sheet name="features" sheetId="22" r:id="rId2"/>
-    <sheet name="core" sheetId="2" r:id="rId3"/>
-    <sheet name="intermed" sheetId="5" r:id="rId4"/>
-    <sheet name="ques" sheetId="6" r:id="rId5"/>
-    <sheet name="-" sheetId="8" r:id="rId6"/>
+    <sheet name="what-how" sheetId="21" r:id="rId1"/>
+    <sheet name="Comps" sheetId="8" r:id="rId2"/>
+    <sheet name="Architect" sheetId="27" r:id="rId3"/>
+    <sheet name="DtEngi" sheetId="29" r:id="rId4"/>
+    <sheet name="Spark" sheetId="23" r:id="rId5"/>
+    <sheet name="Develop" sheetId="32" r:id="rId6"/>
+    <sheet name="Unity" sheetId="26" r:id="rId7"/>
+    <sheet name="OLTP" sheetId="31" r:id="rId8"/>
+    <sheet name="ML" sheetId="30" r:id="rId9"/>
+    <sheet name="core" sheetId="2" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="352">
   <si>
     <t>Azure Databrick</t>
   </si>
@@ -40,13 +44,969 @@
     <t>https://docs.databricks.com/aws/en/introduction/</t>
   </si>
   <si>
-    <t>Databricks is a unified, open analytics platform for building, deploying, sharing, and maintaining enterprise-grade data, analytics, and AI solutions at scale. The Databricks Data Intelligence Platform integrates with cloud storage and security in your cloud account, and manages and deploys cloud infrastructure for you.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Databricks is a unified, open analytics platform for building, deploying, sharing, and maintaining enterprise-grade data, analytics, and AI solutions at scale. The Databricks Data Intelligence Platform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">integrates with cloud storage and security in your cloud account, and manages and deploys cloud infrastructure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>for you.</t>
+    </r>
   </si>
   <si>
     <t>Databricks uses generative AI with the data lakehouse to understand the unique semantics of your data. Then, it automatically optimizes performance and manages infrastructure to match your business needs.</t>
   </si>
   <si>
-    <t>Natural language processing learns your business's language, so you can search and discover data by asking a question in your own words. Natural language assistance helps you write code, troubleshoot errors, and find answers in documentation.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Natural language processing learns your business's language, so you can search and discover data by asking a question in your own words</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>. Natural language assistance helps you write code, troubleshoot errors, and find answers in documentation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Data lakehouse?  // Explained more  topics of DtLake, DtWarehouse DtLakehouse, DtMart, DtMesh, DtFabric at end of this sheet</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/</t>
+  </si>
+  <si>
+    <t>A data lakehouse is a data management system that combines the benefits of data lakes and data warehouses</t>
+  </si>
+  <si>
+    <t>A data lakehouse provides scalable storage and processing capabilities for modern organizations that want to avoid isolated systems for processing different workloads, like machine learning (ML) and business intelligence (BI). A data lakehouse can help establish a single source of truth, eliminate redundant costs, and ensure data freshness.
+Data lakehouses often use a data design pattern that incrementally improves, enriches, and refines data as it moves through layers of staging and transformation. Each layer of the lakehouse can include one or more layers. This pattern is frequently referred to as a medallion architecture</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/medallion</t>
+  </si>
+  <si>
+    <t>How does the Databricks lakehouse work?</t>
+  </si>
+  <si>
+    <t>Databricks is built on Apache Spark. Apache Spark enables a massively scalable engine that runs on compute resources decoupled from storage</t>
+  </si>
+  <si>
+    <t>The Databricks lakehouse uses two additional key technologies:</t>
+  </si>
+  <si>
+    <t>Delta Lake: an optimized storage layer that supports ACID transactions and schema enforcement.</t>
+  </si>
+  <si>
+    <t>Unity Catalog: a unified, fine-grained governance solution for data and AI.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Stage 1: Data ingestion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+At the ingestion layer, batch or streaming data arrives from a variety of sources and in a variety of formats. This first logical layer provides a place for that data to land in its raw format. As you convert those files to Delta tables, you can use the schema enforcement capabilities of Delta Lake to check for missing or unexpected data. You can use Unity Catalog to register tables according to your data governance model and required data isolation boundaries. Unity Catalog allows you to track the lineage of your data as it is transformed and refined, as well as apply a unified governance model to keep sensitive data private and secure.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Stage 2: Data processing, curation, and integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+Once verified, you can start curating and refining your data. Data scientists and machine learning practitioners frequently work with data at this stage to start combining or creating new features and complete data cleansing. Once your data has been thoroughly cleansed, it can be integrated and reorganized into tables designed to meet your particular business needs.
+A schema-on-write approach, combined with Delta schema evolution capabilities, means that you can make changes to this layer without necessarily having to rewrite the downstream logic that serves data to your end users.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Stage 3: Data serving</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+The final layer serves clean, enriched data to end users. The final tables should be designed to serve data for all your use cases. A unified governance model means you can track data lineage back to your single source of truth. Data layouts, optimized for different tasks, allow end users to access data for machine learning applications, data engineering, and business intelligence and reporting.
+To learn more about Delta Lake, see What is Delta Lake in Azure Databricks? To learn more about Unity Catalog, see What is Unity Catalog?</t>
+    </r>
+  </si>
+  <si>
+    <t>Capabilities of a Databricks lakehouse</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/#capabilities-of-a-databricks-lakehouse</t>
+  </si>
+  <si>
+    <t>What are all the Delta things in Azure Databricks?</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/introduction/delta-comparison</t>
+  </si>
+  <si>
+    <t>Delta refers to technologies related to or in the Delta Lake open source project</t>
+  </si>
+  <si>
+    <t>https://delta.io/</t>
+  </si>
+  <si>
+    <t>An open-source storage framework that enables building a Lakehouse architecture with compute engines including Spark, PrestoDB, Flink, Trino, and Hive and APIs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>unified data management system for handling transactional real-time and batch big data, by extending Parquet data files with a file-based transaction log for ACID transactions and scalable metadata handling.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Apache Parquet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> is an open source, column-oriented data file format designed for efficient data storage and retrieval. It provides efficient data compression and encoding schemes with enhanced performance to handle complex data in bulk. Apache Parquet is designed to be a common interchange format for both batch and interactive workloads. It is similar to other columnar-storage file formats available in Hadoop, namely RCFile and ORC.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Key Features of DELTA LAKE:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+ACID Transactions: Protect your data with serializability, the strongest level of isolation
+Scalable Metadata: Handle petabyte-scale tables with billions of partitions and files with ease
+Time Travel: Access/revert to earlier versions of data for audits, rollbacks, or reproduce
+Open Source: Community driven, open standards, open protocol, open discussions
+Unified Batch/Streaming: Exactly once semantics ingestion to backfill to interactive queries
+Schema Evolution / Enforcement: Prevent bad data from causing data corruption
+Audit History: Delta Lake log all change details providing a fill audit trail
+DML Operations: SQL, Scala/Java and Python APIs to merge, update and delete datasets</t>
+    </r>
+  </si>
+  <si>
+    <t>Delta table is the default data table format in Azure Databricks and is a feature of the Delta Lake open source data framework. Delta tables are typically used for data lakes, where data is ingested via streaming or in large batches.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/introduction/delta-comparison#lakeflow-declarative-pipelines-data-pipelines</t>
+  </si>
+  <si>
+    <t>Delta tables vs. Lakeflow Declarative Pipelines</t>
+  </si>
+  <si>
+    <t>Delta table is a way to store data in tables, whereas Lakeflow Declarative Pipelines allows you to describe how data flows between these tables declaratively. Lakeflow Declarative Pipelines is a declarative framework that manages many delta tables, by creating them and keeping them up to date. In short, Delta tables is a data table architecture while Lakeflow Declarative Pipelines is a data pipeline framework.</t>
+  </si>
+  <si>
+    <t>Delta Sharing
+An open standard for secure data sharing, Delta Sharing enables data sharing between organizations regardless of their compute platform.
+Delta engine
+A query optimizer for big data that uses Delta Lake open source technology included in Databricks. Delta engine optimizes the performance of Spark SQL, Databricks SQL, and DataFrame operations by pushing computation to the data.
+Delta Lake transaction log (AKA DeltaLogs)
+A single source of truth tracking all changes that users make to the table and the mechanism through which Delta Lake guarantees atomicity. See the Delta transaction log protocol on GitHub.</t>
+  </si>
+  <si>
+    <t>Lakehouse vs Data Lake vs Data Warehouse &amp; Data Mart vs Data Mesh</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/#lakehouse-vs-data-lake-vs-data-warehouse</t>
+  </si>
+  <si>
+    <t>https://azure.microsoft.com/en-us/resources/cloud-computing-dictionary/what-is-a-data-lake</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Data Mesh: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>https://aws.amazon.com/compare/the-difference-between-a-data-warehouse-data-lake-and-data-mart/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Data Fabric: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>https://appian.com/learn/topics/data-fabric/data-fabric-vs-data-mesh-vs-data-lake</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Data warehouse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>A data warehouse is a specialized database system designed for the storage, retrieval, and analysis of structured data. It serves as a central repository for an organization’s historical data, primarily focusing on structured and well-defined data sources.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+As data warehouses are used to store historical data for analysis and reporting, they consolidate structured data from multiple sources and optimize query performance with techniques such as indexing and partitioning. Before ingesting the data, data warehouses use ETL procedures to structure and transform data to ensure consistency and quality.
+When it comes to storing the data in a data warehouse, it’s stored in either a columnar or row-based format.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Using data marts, which are subsets of data focused on specific business areas for efficient retrieval,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> star or snowflake schema models organize data for complex queries with multiple dimensions and measures. They also use SQL for queries and OLAP for multidimensional analysis.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.connectwise.com/blog/data-warehouse-vs-data-lake-vs-data-lakehouse-vs-data-mesh-a-comprehensive-comparison</t>
+  </si>
+  <si>
+    <t>Data lake</t>
+  </si>
+  <si>
+    <t>A data lake is a central repository for storing vast amounts of raw, semi-structured, and unstructured data at scale. Unlike traditional databases, data lakes are designed to handle data in its native format without the need for prior structuring.</t>
+  </si>
+  <si>
+    <t>Data lakes store raw and untransformed data, and they’re highly scalable for big data and IoT applications. Schema-on-read allows for flexible data exploration, and they can handle large amounts of data from diverse sources using distributed file systems or cloud-based storage. Partitioning can also help to improve query performance.</t>
+  </si>
+  <si>
+    <t>Data lakes use schema-on-read to transform and structure data for analysis. Common processing frameworks, like Apache Spark, are used for data processing and analysis. Data lakes are great for machine learning and data science.</t>
+  </si>
+  <si>
+    <t>Data lakes simplify data exploration by enabling users to extract insights from raw data before structuring it. They support advanced analytics like predictive modeling, anomaly detection, and sentiment analysis, and they can be integrated with data lakehouse architectures for structured querying.</t>
+  </si>
+  <si>
+    <t>Data lakes come in two types: on-premises and cloud-based. Apache Hadoop and HDFS are often used for on-premises data lakes, while AWS Data Lake, Azure Data Lake Storage, and Google Cloud Storage are some of the more popular cloud-based options.</t>
+  </si>
+  <si>
+    <t>Data Lakehouse</t>
+  </si>
+  <si>
+    <t>A data lakehouse is a relatively new and hybrid data architecture that aims to combine the benefits of both data lakes and data warehouses. It addresses the need for scalable storage, schema-on-read flexibility, and structured querying capabilities.</t>
+  </si>
+  <si>
+    <t>The data lakehouse approach combines the strengths of data lakes and data warehouses. It can store both structured and semi-structured data, and it uses advanced technologies, such as Delta Lake or Apache Iceberg, for schema evolution and data versioning. It often uses distributed file systems or cloud-based storage for unified storage.</t>
+  </si>
+  <si>
+    <t>Since data lakehouses handle both raw and structured data, they use ETL and ELT processes to transform and load data for analytical querying. Data lakehouses support advanced querying with SQL, making them compatible with a range of analytics tools and frameworks. Some also enable time-travel queries for historical analysis.</t>
+  </si>
+  <si>
+    <t>They’re great for data science and machine learning projects, as they have the ability to scale to meet growing data needs. Just look at Delta Lake and Apache Iceberg, which have brought ACID transactions, schema evolution, and time-travel features to big data workloads.</t>
+  </si>
+  <si>
+    <t>Data lakehouses are flexible and versatile, combining the benefits of data lakes with structured querying capabilities. This allows for diverse data usage and easy adaptation to changing data requirements. They also offer a unified storage solution for both raw and structured data, making data management simpler—which is ideal for various analytics, from basic reporting to advanced data science.</t>
+  </si>
+  <si>
+    <t>However, compared to traditional data warehouses, data lakehouse architecture requires careful planning and management, with additional overhead for ACID transactions and time-travel features. Schema-on-read and schema-on-write may also require adjustment.</t>
+  </si>
+  <si>
+    <t>Data mesh: Data Mesh is a paradigm, while lakehouse is a platform. Data mesh is focused on solving scalability of data ownership</t>
+  </si>
+  <si>
+    <t>Data mesh is a modern data architecture and organizational approach that aims to address the challenges of scaling and democratizing data within large, complex organizations. It represents a shift away from a centralized data approach to a more decentralized, domain-oriented model.</t>
+  </si>
+  <si>
+    <t>Data mesh promotes decentralized data ownership and management across domains. It encourages cross-functional teams to treat data as a product and take responsibility for its quality and governance, creating a data fabric that facilitates data discovery, access, and sharing.</t>
+  </si>
+  <si>
+    <t>Treating data as a product emphasizes the importance of quality, usability, and accountability. Data producers need to understand the needs of their data consumers and provide data in a user-friendly and accessible manner. This principle encourages data teams to focus on delivering value to the organization through their data products.</t>
+  </si>
+  <si>
+    <t>implementing a data mesh requires organizational changes like new team structures. A clear strategy and governance framework are also crucial to managing this architecture. Plus, keeping the data catalog up-to-date can be challenging in rapidly evolving organizations.</t>
+  </si>
+  <si>
+    <t>Data Fabric</t>
+  </si>
+  <si>
+    <t>https://appian.com/learn/topics/data-fabric/data-fabric-vs-data-mesh-vs-data-lake</t>
+  </si>
+  <si>
+    <t>A data fabric includes a virtualization layer, a concept that you may also see referred to as a “logical data warehouse.” This means that with a data fabric, disparate system data is virtualized into a centralized platform, complete with the ability to connect, relate, and extend data. You might also think of data fabric as an abstraction layer for managing your data. A key point to remember about using a data fabric: the data stays where it is; it does not move out of the source systems.</t>
+  </si>
+  <si>
+    <t>With data fabric, we do not need to hook into the system-to-system API calls directly in order to access data—the APIs are abstracted away. This abstraction lets us take advantage of the data in different systems without needing to know what the source system is or how to connect to it. The data may be on-premises or it may be in a cloud service like AWS as part of your hybrid cloud strategy.</t>
+  </si>
+  <si>
+    <t>Whereas data mesh requires software specialists, data fabric enables any number of line-of-business people on your teams to work with data modeling—not just developers. That means non-technical employees can use low-code tools to do data modeling work themselves, which leads to increased speed and agility.</t>
+  </si>
+  <si>
+    <t>What about the governance challenges? As noted earlier, data mesh poses challenges related to observability and maintenance because of its distributed nature. In contrast, data fabric is centralized. With data fabric keeping all your data in one virtualized data model, you get a complete, unified view of all your different systems. Even if certain patterns have not been used before, relating the data in the virtualized model allows for new modes of data access to be implemented easily and in a governable way.</t>
+  </si>
+  <si>
+    <t>Here’s a hint for discussing data fabric with others: The term “data fabric” can refer either to the architecture layer where the data virtualization happens or to the toolset that you use there.</t>
+  </si>
+  <si>
+    <t>The use of a data virtualization layer is a strong value add on its own. But this value increases greatly when you marry your virtualized data model with your business applications on a process automation platform with low-code capabilities and record-level security. For example, using low-code security rules, you can reference data in your CRM to enforce whether specific rows of data from your ERP should be accessible. You can also calculate custom data fields, like SLAs, by referencing customer data and case data, even if they aren’t located in the same system. Features like these allow you to maximize your business potential without forsaking your existing systems or technologies. This approach also builds in flexibility for the future.</t>
+  </si>
+  <si>
+    <t>Data Swamp</t>
+  </si>
+  <si>
+    <t>https://medium.com/@soumyaranjan0408/navigating-the-data-landscape-understanding-data-warehouse-data-lake-data-lakehouse-data-mesh-f8608b23016d</t>
+  </si>
+  <si>
+    <t>A data swamp is a conceptual state of disorganized and poorly managed data repository characterized by inadequate governance, quality, and usability. Unlike a data lake, which is designed to store and manage data effectively, a data swamp lacks structure, metadata management, and governance controls, leading to difficulties in data discovery, trust, and utilization.</t>
+  </si>
+  <si>
+    <t>Azure Databricks components</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/getting-started/concepts</t>
+  </si>
+  <si>
+    <t>Accounts and workspaces</t>
+  </si>
+  <si>
+    <t>Billing: Databricks units (DBUs)</t>
+  </si>
+  <si>
+    <t>Authentication and authorization</t>
+  </si>
+  <si>
+    <t>Azure Databricks interfaces</t>
+  </si>
+  <si>
+    <t>REST API</t>
+  </si>
+  <si>
+    <t>The Databricks REST API provides endpoints for modifying or requesting information about Azure Databricks account and workspace objects</t>
+  </si>
+  <si>
+    <t>SQL REST API</t>
+  </si>
+  <si>
+    <t>The SQL REST API allows you to automate tasks on SQL objects</t>
+  </si>
+  <si>
+    <t>https://docs.databricks.com/api/azure/workspace/statementexecution</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dev-tools/sql-execution-tutorial</t>
+  </si>
+  <si>
+    <t>Limits and limitations</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>The Databricks CLI is hosted on GitHub. The CLI is built on top of the Databricks REST API.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dev-tools/cli/</t>
+  </si>
+  <si>
+    <t>Data management</t>
+  </si>
+  <si>
+    <t>Database objects in Azure Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/database-objects/</t>
+  </si>
+  <si>
+    <t>Unity Catalog</t>
+  </si>
+  <si>
+    <t>Unity Catalog is a unified governance solution for data and AI assets on Azure Databricks that provides centralized access control, auditing, lineage, and data discovery capabilities across Databricks workspaces</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/</t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t>Catalogs are the highest level container for organizing and isolating data on Azure Databricks. You can share catalogs across workspaces within the same region and account</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/catalogs/</t>
+  </si>
+  <si>
+    <t>Schema</t>
+  </si>
+  <si>
+    <t>Schemas, also known as databases, are contained within catalogs and provide a more granular level of organization. They contain database objects and AI assets, such as volumes, tables, functions, and models</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/schemas/</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Tables organize and govern access to structured data. You query tables with Apache Spark SQL and Apache Spark APIs.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/tables/</t>
+  </si>
+  <si>
+    <t>View</t>
+  </si>
+  <si>
+    <t>A view is a read-only object derived from one or more tables and views. Views save queries that are defined against tables</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Volumes represent a logical volume of storage in a cloud object storage location and organize and govern access to non-tabular data. Databricks recommends using volumes for managing all access to non-tabular data on cloud object storage.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/volumes/</t>
+  </si>
+  <si>
+    <t>Delta table</t>
+  </si>
+  <si>
+    <t>By default, all tables created in Azure Databricks are Delta tables. Delta tables are based on the Delta Lake open source project, a framework for high-performance ACID table storage over cloud object stores. A Delta table stores data as a directory of files on cloud object storage and registers table metadata to the metastore within a catalog and schema.</t>
+  </si>
+  <si>
+    <t>Metastore</t>
+  </si>
+  <si>
+    <t>Unity Catalog provides an account-level metastore that registers metadata about data, AI, and permissions about catalogs, schemas, and tables.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/#metastore</t>
+  </si>
+  <si>
+    <t>Azure Databricks provides a legacy Hive metastore for customers that have not adopted Unity Catalog</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/table-acls/</t>
+  </si>
+  <si>
+    <t>Catalog Explorer</t>
+  </si>
+  <si>
+    <t>Catalog Explorer allows you to explore and manage data and AI assets, including schemas (databases), tables, models, volumes (non-tabular data), functions, and registered ML models. You can use it to find data objects and owners, understand data relationships across tables, and manage permissions and sharing</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/catalog-explorer/</t>
+  </si>
+  <si>
+    <t>DBFS root</t>
+  </si>
+  <si>
+    <t>Storing and accessing data using DBFS root or DBFS mounts is a deprecated pattern and not recommended by Databricks. Instead, Databricks recommends using Unity Catalog to manage access to all data</t>
+  </si>
+  <si>
+    <t>The DBFS root is a storage location available to all users by default.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dbfs/</t>
+  </si>
+  <si>
+    <t>Computation management</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>A set of computation resources and configurations on which you run notebooks and jobs. There are two types of clusters: all-purpose and job</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/compute/</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>You create an all-purpose cluster using the UI, CLI, or REST API. You can manually terminate and restart an all-purpose cluster. Multiple users can share such clusters to do collaborative interactive analysis.</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>The Azure Databricks job scheduler creates a job cluster when you run a job on a new job cluster and terminates the cluster when the job is complete. You cannot restart an job cluster.</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>A set of idle, ready-to-use instances that reduce cluster start and auto-scaling times. When attached to a pool, a cluster allocates its driver and worker nodes from the pool.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/compute/pools</t>
+  </si>
+  <si>
+    <t>If the pool does not have sufficient idle resources to accommodate the cluster's request, the pool expands by allocating new instances from the instance provider. When an attached cluster is terminated, the instances it used are returned to the pool and can be reused by a different cluster.</t>
+  </si>
+  <si>
+    <t>Databricks runtime</t>
+  </si>
+  <si>
+    <t>The set of core components that run on the clusters managed by Azure Databricks. See Compute. Azure Databricks has the following runtimes:</t>
+  </si>
+  <si>
+    <t>Databricks Runtime includes Apache Spark but also adds a number of components and updates that substantially improve the usability, performance, and security of big data analytics.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Databricks Runtime for Machine Learning is built on Databricks Runtime and provides prebuilt machine learning infrastructure that is integrated with all of the capabilities of the Azure Databricks workspace. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>It contains multiple popular libraries, including TensorFlow, Keras, PyTorch, and XGBoost.</t>
+    </r>
+  </si>
+  <si>
+    <t>Jobs &amp; Pipelines UI</t>
+  </si>
+  <si>
+    <t>The Jobs &amp; Pipelines workspace UI provides entry to the Jobs, Lakeflow Declarative Pipelines, and Lakeflow Connect UIs, which are tools that allow you to orchestrate and schedule workflows.</t>
+  </si>
+  <si>
+    <t>Jobs</t>
+  </si>
+  <si>
+    <t>A non-interactive mechanism for orchestrating and scheduling notebooks, libraries, and other tasks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/jobs/</t>
+  </si>
+  <si>
+    <t>Pipelines</t>
+  </si>
+  <si>
+    <t>Lakeflow Declarative Pipelines provide a declarative framework for building reliable, maintainable, and testable data processing pipelines</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dlt/</t>
+  </si>
+  <si>
+    <t>Workload</t>
+  </si>
+  <si>
+    <t>Workload is the amount of processing capability needed to perform a task or group of tasks. Azure Databricks identifies two types of workloads: data engineering (job) and data analytics (all-purpose).</t>
+  </si>
+  <si>
+    <t>Data engineering An (automated) workload runs on a job cluster which the Azure Databricks job scheduler creates for each workload.</t>
+  </si>
+  <si>
+    <t>Data analytics An (interactive) workload runs on an all-purpose cluster. Interactive workloads typically run commands within an Azure Databricks notebook. However, running a job on an existing all-purpose cluster is also treated as an interactive workload.</t>
+  </si>
+  <si>
+    <t>Execution context</t>
+  </si>
+  <si>
+    <t>The state for a read–eval–print loop (REPL) environment for each supported programming language. The languages supported are Python, R, Scala, and SQL.</t>
+  </si>
+  <si>
+    <t>Data engineering</t>
+  </si>
+  <si>
+    <t>Data engineering tools aid collaboration among data scientists, data engineers, data analysts, and machine learning engineers.</t>
+  </si>
+  <si>
+    <t>Workspace</t>
+  </si>
+  <si>
+    <t>A workspace is an environment for accessing all of your Azure Databricks assets. A workspace organizes objects (notebooks, libraries, dashboards, and experiments) into folders and provides access to data objects and computational resources.</t>
+  </si>
+  <si>
+    <t>Notebook</t>
+  </si>
+  <si>
+    <t>A web-based interface for creating data science and machine learning workflows that can contain runnable commands, visualizations, and narrative text. See Databricks notebooks.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/notebooks/</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>A package of code available to the notebook or job running on your cluster. Databricks runtimes include many libraries, and you can also upload your own</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/libraries/</t>
+  </si>
+  <si>
+    <t>Git folder (formerly Repos)</t>
+  </si>
+  <si>
+    <t>A folder whose contents are co-versioned together by syncing them to a remote Git repository. Databricks Git folders integrate with Git to provide source and version control for your projects.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/repos/</t>
+  </si>
+  <si>
+    <t>AI and machine learning</t>
+  </si>
+  <si>
+    <t>Databricks provides an integrated end-to-end environment with managed services for developing and deploying AI and machine learning applications.</t>
+  </si>
+  <si>
+    <t>Mosaic AI</t>
+  </si>
+  <si>
+    <t>The brand name for products and services from Databricks Mosaic AI Research, a team of researchers and engineers responsible for Databricks biggest breakthroughs in generative AI. Mosaic AI products include the ML and AI features in Databricks</t>
+  </si>
+  <si>
+    <t>https://www.databricks.com/research/mosaic</t>
+  </si>
+  <si>
+    <t>Machine learning runtime</t>
+  </si>
+  <si>
+    <t>To help you develop ML and AI models, Databricks provides a Databricks Runtime for Machine Learning, which automates compute creation with pre-built machine learning and deep learning infrastructure including the most common ML and DL libraries. It also has built-in, pre-configured GPU support including drivers and supporting libraries. Browse to information about the latest runtime releases from Databricks Runtime release notes versions and compatibility.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/release-notes/runtime/</t>
+  </si>
+  <si>
+    <t>Experiment</t>
+  </si>
+  <si>
+    <t>A collection of MLflow runs for training a machine learning model. See Organize training runs with MLflow experiments.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/mlflow/tracking</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/mlflow/experiments</t>
+  </si>
+  <si>
+    <t>Create experiment from the Experiments page</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Foundation Model Fine-tuning. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The Foundation Model Fine-tuning dialog appears. For details, see Create a training run using the Foundation Model Fine-tuning UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Forecasting.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> The Configure Forecasting experiment dialog appears. For details, see Configure the AutoML experiment.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Classification.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> The Configure Classification experiment dialog appears. For details, see Set up classification experiment with the UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Regression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>. The Configure Classification experiment dialog appears. For details, see Set up regression experiment with the UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Custom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>. The Create MLflow Experiment dialog appears. For details, see Step 4 in Create experiment from the workspace.</t>
+    </r>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Features are an important component of ML models. A feature store enables feature sharing and discovery across your organization and also ensures that the same feature computation code is used for model training and inference</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/machine-learning/feature-store/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In machine learning, features are the individual, measurable properties or characteristics of a phenomenon being observed that are used as input variables to a model. Essentially, they are the data points that a machine learning model uses to learn and make predictions. </t>
+  </si>
+  <si>
+    <t>Generative AI models</t>
+  </si>
+  <si>
+    <t>Databricks supports the exploration, development, and deployment of generative AI models, including:</t>
+  </si>
+  <si>
+    <t>AI playground, a chat-like environment in the workspace where you can test, prompt, and compare LLMs. See Chat with LLMs and prototype generative AI apps using AI Playground.</t>
+  </si>
+  <si>
+    <t>A built-in set of pre-configured foundation models that you can query:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    See Pay-per-token Foundation Model APIs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     See [Recommended] Deploy foundation models from Unity Catalog for foundation models you can serve with a single click.</t>
+  </si>
+  <si>
+    <t>Third-party hosted LLMs, called external models. These models are meant to be used as-is.</t>
+  </si>
+  <si>
+    <t>Capabilities to customize a foundation model to optimize its performance for your specific application (often called fine-tuning). See Foundation Model Fine-tuning.</t>
+  </si>
+  <si>
+    <t>Model registry</t>
+  </si>
+  <si>
+    <t>Databricks provides a hosted version of MLflow Model Registry in Unity Catalog. Models registered in Unity Catalog inherit centralized access control, lineage, and cross-workspace discovery and access</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/machine-learning/manage-model-lifecycle/</t>
+  </si>
+  <si>
+    <t>Model serving</t>
+  </si>
+  <si>
+    <t>Mosaic AI Model Serving provides a unified interface to deploy, govern, and query AI models. Each model you serve is available as a REST API that you can integrate into your web or client application. With Mosaic AI Model Serving, you can deploy your own models, foundation models, or third-party models hosted outside of Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/machine-learning/model-serving/</t>
+  </si>
+  <si>
+    <t>Data warehousing</t>
+  </si>
+  <si>
+    <t>Data warehousing refers to collecting and storing data from multiple sources so it can be quickly accessed for business insights and reporting. Databricks SQL is the collection of services that bring data warehousing capabilities and performance to your existing data lakes.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/sql/get-started/data-warehousing-concepts</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>A query is a valid SQL statement that allows you to interact with your data. You can author queries using the in-platform SQL editor, or connect using a SQL connector, driver, or API</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/sql/user/queries/</t>
+  </si>
+  <si>
+    <t>SQL warehouse</t>
+  </si>
+  <si>
+    <t>A computation resource on which you run SQL queries. There are three types of SQL warehouses: Classic, Pro, and Serverless. Azure Databricks recommends using serverless warehouses where available</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/compute/sql-warehouse/warehouse-types</t>
+  </si>
+  <si>
+    <t>Visualization</t>
+  </si>
+  <si>
+    <t>A graphical presentation of the result of running a query.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/visualizations/</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>A presentation of data visualizations and commentary. You can use dashboards to automatically send reports to anyone in your Azure Databricks account. Use the Databricks Assistant to help you build visualizations based on natural language prompts.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dashboards/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/notebooks/dashboards</t>
+  </si>
+  <si>
+    <t>Top features</t>
+  </si>
+  <si>
+    <t>https://complereinfosystem.com/top-10-databricks-features-you-must-explore</t>
   </si>
   <si>
     <t>https://learn.microsoft.com/en-us/azure/databricks/introduction/</t>
@@ -103,10 +1063,544 @@
     <t>https://docs.databricks.com/aws/en/pyspark/#apis-and-libraries</t>
   </si>
   <si>
-    <t>Top features</t>
-  </si>
-  <si>
-    <t>https://complereinfosystem.com/top-10-databricks-features-you-must-explore</t>
+    <t>Azure Databricks architecture</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/getting-started/overview</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/getting-started/overview#architecture</t>
+  </si>
+  <si>
+    <t>High-level architecture</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/compute/#types-of-compute</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/security/network/serverless-network-security/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/security/network/classic/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/getting-started/overview#storage</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/get-started</t>
+  </si>
+  <si>
+    <t>What are ACID guarantees on Azure Databricks?</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/acid</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Azure Databricks uses Delta Lake by default for all reads and writes and builds upon the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ACID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> guarantees provided by the open source Delta Lake protocol. ACID stands for atomicity, consistency, isolation, and durability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Atomicity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> means that all transactions either succeed or fail completely.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Consistency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> guarantees relate to how a given state of the data is observed by simultaneous operations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Isolation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> refers to how simultaneous operations potentially conflict with one another.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Durability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> means that committed changes are permanent.</t>
+    </r>
+  </si>
+  <si>
+    <t>While many data processing and warehousing technologies describe having ACID transactions, specific guarantees vary by system, and transactions on Azure Databricks might differ from other systems you've worked with</t>
+  </si>
+  <si>
+    <t>What is the medallion lakehouse architecture?</t>
+  </si>
+  <si>
+    <t>The medallion architecture describes a series of data layers that denote the quality of data stored in the lakehouse. Azure Databricks recommends taking a multi-layered approach to building a single source of truth for enterprise data products.</t>
+  </si>
+  <si>
+    <t>This architecture guarantees atomicity, consistency, isolation, and durability as data passes through multiple layers of validations and transformations before being stored in a layout optimized for efficient analytics. The terms bronze (raw), silver (validated), and gold (enriched) describe the quality of the data in each of these layers.</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>What happens in this layer?</t>
+  </si>
+  <si>
+    <t>Raw data ingestion</t>
+  </si>
+  <si>
+    <t>Data cleaning and validation</t>
+  </si>
+  <si>
+    <t>Dimensional modeling and aggregation</t>
+  </si>
+  <si>
+    <t>Who is the intended user?</t>
+  </si>
+  <si>
+    <t>Data engineers</t>
+  </si>
+  <si>
+    <t>Business analysts and BI developers</t>
+  </si>
+  <si>
+    <t>Data operations</t>
+  </si>
+  <si>
+    <t>Data analysts (use the Silver layer for a more refined dataset that still retains detailed information necessary for in-depth analysis)</t>
+  </si>
+  <si>
+    <t>Data scientists and machine learning (ML) engineers</t>
+  </si>
+  <si>
+    <t>Compliance and audit teams</t>
+  </si>
+  <si>
+    <t>Data scientists (build models and perform advanced analytics)</t>
+  </si>
+  <si>
+    <t>Executives and decision makers</t>
+  </si>
+  <si>
+    <t>Operational teams</t>
+  </si>
+  <si>
+    <t>What does it mean to build a single source of truth?</t>
+  </si>
+  <si>
+    <t>The Databricks lakehouse eliminates the need for creating and syncing copies of data across multiple systems by unifying data access and storage in a single system, establishing the lakehouse as the single source of truth (SSOT). Duplicating data often results in data silos, meaning that different teams within an organization may be working with versions of the same data that differ in quality and freshness.</t>
+  </si>
+  <si>
+    <t>How does the lakehouse control transactions and data access?</t>
+  </si>
+  <si>
+    <t>Delta Lake transactions use log files stored alongside data files to provide ACID guarantees at a table level. Because the data and log files backing Delta Lake tables live together in cloud object storage, reading and writing data can occur simultaneously without risk of many queries resulting in performance degradation or deadlock for business-critical workloads. This means that users and applications throughout the enterprise environment can connect to the same single copy of the data to drive diverse workloads, with all viewers guaranteed to receive the most current version of the data at the time their query executes.</t>
+  </si>
+  <si>
+    <t>Leverage views in the lakehouse</t>
+  </si>
+  <si>
+    <t>Views on Azure Databricks represent saved queries against data stored in tables somewhere in the lakehouse. Whereas the queries that result in tables are executed at write time, views execute defining logic each time a query against a view runs. This means that views can provide up-to-date access to data from a variety of sources, and that compute is only spent to update results as they are needed.</t>
+  </si>
+  <si>
+    <t>You can use Unity Catalog to secure and share views alongside other data objects, allowing individuals and teams to share the logic that drives key business decisions across the organization.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/views/</t>
+  </si>
+  <si>
+    <t>Data discovery and collaboration in the lakehouse</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse/collaboration</t>
+  </si>
+  <si>
+    <t>Databricks designed Unity Catalog to help organizations reduce time to insights by empowering a broader set of data users to discover and analyze data at scale. Data stewards can securely grant access to data assets for diverse teams of end users in Unity Catalog. These users can then use a variety of languages and tools, including SQL and Python, to create derivative datasets, models, and dashboards that can be shared across teams.</t>
+  </si>
+  <si>
+    <t>Manage permissions at scale</t>
+  </si>
+  <si>
+    <t>Discover data on Azure Databricks</t>
+  </si>
+  <si>
+    <t>Accelerate time to production with the lakehouse</t>
+  </si>
+  <si>
+    <t>Lakehouse architecture</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/</t>
+  </si>
+  <si>
+    <t>Introduction to the well-architected data lakehouse</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/#articles-about-lakehouse-architecture</t>
+  </si>
+  <si>
+    <t>The scope of the lakehouse</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/scope#a-modern-data-and-ai-platform-framework</t>
+  </si>
+  <si>
+    <t>Guiding principles for the lakehouse</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/guiding-principles</t>
+  </si>
+  <si>
+    <t>Ground rules that define and influence your architecture. They explain the vision behind a lakehouse implementation and form the basis for future decisions on your data, analytics, and AI architecture.</t>
+  </si>
+  <si>
+    <t>Downloadable lakehouse reference architectures</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/reference</t>
+  </si>
+  <si>
+    <t>Downloadable architecture blueprints outline the recommended setup of the Databricks Data Intelligence Platform and its integration with cloud providers' services</t>
+  </si>
+  <si>
+    <t>The seven pillars of the well-architected lakehouse, their principles, and best practices</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/lakehouse-architecture/well-architected</t>
+  </si>
+  <si>
+    <t>Understand the pros and cons of decisions you make when building the lakehouse. This framework provides architectural best practices for developing and operating a safe, reliable, efficient, and cost-effective lakehouse</t>
+  </si>
+  <si>
+    <t>Data engineering with Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/</t>
+  </si>
+  <si>
+    <t>Databricks provides Lakeflow, an end-to-end data engineering solution that empowers data engineers, software developers, SQL developers, analysts, and data scientists to deliver high-quality data for downstream analytics, AI, and operational applications. Lakeflow is a unified solution for ingestion, transformation, and orchestration of your data, and includes Lakeflow Connect, Lakeflow Declarative Pipelines, and Lakeflow Jobs</t>
+  </si>
+  <si>
+    <t>Data engineering concepts</t>
+  </si>
+  <si>
+    <t>Procedural vs. declarative data processing in Azure Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/procedural-vs-declarative</t>
+  </si>
+  <si>
+    <t>Procedural data processing</t>
+  </si>
+  <si>
+    <t>Procedural data processing follows a structured approach where explicit steps are defined to manipulate data. This model is closely aligned with imperative programming, emphasizing a command sequence that dictates how the data should be processed.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Characteristics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of procedural processing:
+Step-by-step execution: The developer explicitly defines the order of operations.
+Use of control structures: Loops, conditionals, and functions manage execution flow.
+Detailed resource control: Enables fine-grained optimizations and manual performance tuning.
+Related concepts: Procedural programming is a sub-class of imperative programming.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for procedural processing:
+Custom ETL pipelines requiring procedural logic.
+Low-level performance optimizations in batch and streaming workflows.
+Legacy systems or existing imperative scripts.</t>
+    </r>
+  </si>
+  <si>
+    <t>Declarative data processing</t>
+  </si>
+  <si>
+    <t>Declarative data processing abstracts the how and focuses on defining the desired result. Instead of specifying step-by-step instructions, developers define transformation logic, and the system determines the most efficient execution plan.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Characteristics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of declarative processing:
+Abstraction of execution details: Users describe the desired outcome, not the steps to achieve it.
+Automatic optimization: The system applies query planning and execution tuning.
+Reduced complexity: Removes the need for explicit control structures, improving maintainability.
+Related concepts: Declarative programming includes domain-specific and functional programming paradigms.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for declarative processing:
+SQL-based transformations in batch and streaming workflows.
+High-level data processing frameworks such as Lakeflow Declarative Pipelines.
+Scalable, distributed data workloads requiring automated optimizations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lakeflow Declarative Pipelines is a declarative framework</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> designed to simplify the creation of reliable and maintainable stream processing pipelines. By specifying what data to ingest and how to transform it, Lakeflow Declarative Pipelines automates key aspects of pipeline management, including orchestration, compute management, monitoring, data quality enforcement, and error handling.</t>
+    </r>
+  </si>
+  <si>
+    <t>Key differences: procedural vs. declarative processing</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/procedural-vs-declarative#key-differences-procedural-vs-declarative-processing</t>
+  </si>
+  <si>
+    <t>When to choose procedural or declarative processing</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/procedural-vs-declarative#when-to-choose-procedural-or-declarative-processing</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Structured Streaming</t>
+  </si>
+  <si>
+    <t>Structured Streaming is an API for incremental stream processing in near real-time. It provides strong performance, scalability, and fault tolerance.</t>
+  </si>
+  <si>
+    <t>Lakeflow Declarative Pipelines</t>
+  </si>
+  <si>
+    <t>Lakeflow Declarative Pipelines builds on Structured Streaming, offering a more declarative framework for creating data pipelines. You can define the transformations to perform on your data, and Lakeflow Declarative Pipelines manages orchestration, monitoring, data quality, errors, and more. Therefore, it offers more automation and less overhead than Structured Streaming.</t>
+  </si>
+  <si>
+    <t>Fully-managed connectors</t>
+  </si>
+  <si>
+    <t>Fully-managed connectors build on Lakeflow Declarative Pipelines, offering even more automation for the most popular data sources. They extend Lakeflow Declarative Pipelines functionality to also include source-specific authentication, CDC, edge case handling, long-term API maintenance, automated retries, automated schema evolution, and so on. Therefore, they offer even more automation for any supported data sources.</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Lakehouse Federation</t>
+  </si>
+  <si>
+    <t>Allows you to query external data sources without moving your data.</t>
+  </si>
+  <si>
+    <t>Delta Sharing</t>
+  </si>
+  <si>
+    <t>Allows you to securely share data across platforms, clouds, and regions</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/spark/</t>
+  </si>
+  <si>
+    <t>OLTP Database</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/oltp/</t>
+  </si>
+  <si>
+    <t>Azure Databricks Lakebase, a fully managed Postgres OLTP database engine, integrated into the Databricks Data Intelligence Platform. A database instance is a type of Azure Databricks compute that provides the storage and compute for running a Postgres server that manages multiple databases.</t>
+  </si>
+  <si>
+    <t>An online transaction processing (OLTP) database is a specialized type of database system designed to efficiently handle high volumes of real-time transactional data. Lakebase allows you to create an OLTP database on Azure Databricks, and integrate OLTP workloads with your Lakehouse. This OLTP database enables you to create and manage databases stored in Databricks-managed storage.</t>
+  </si>
+  <si>
+    <t>Using an OLTP database in conjunction with the Azure Databricks platform significantly reduces application complexity. Lakebase is well integrated with Feature management, SQL warehouses, and Databricks Apps. Using sync tables provides a simple and performant way to sync data between OLTP and online analytical processing (OLAP) workloads.</t>
+  </si>
+  <si>
+    <t>Based on Postgres and fully integrated with the Databricks Data Intelligence Platform, Lakebase inherits several core platform capabilities, including:</t>
+  </si>
+  <si>
+    <t>Simplified management: Leverages existing Azure Databricks infrastructure to deploy instances with decoupled compute and storage, managed change data capture with Delta Lake, and support for multi-cloud deployments.</t>
+  </si>
+  <si>
+    <t>Integrated artificial intelligence (AI) and machine learning (ML) capabilities: Supports feature and model serving, retrieval-augmented generation (RAG), and other AI and ML integrations.</t>
+  </si>
+  <si>
+    <t>Integrated authentication and governance: Optionally, use Unity Catalog to enforce secure access to data.</t>
   </si>
   <si>
     <t>Most basic things in py</t>
@@ -155,31 +1649,13 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF080808"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -200,8 +1676,33 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -213,9 +1714,22 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <i/>
       <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Inter"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -564,27 +2078,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD1D5DA"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD1D5DA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFD1D5DA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD1D5DA"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -703,31 +2202,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -736,148 +2223,201 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,15 +2484,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>62865</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>294640</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>189230</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3801745</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -969,8 +2509,267 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="419100" y="816610"/>
-          <a:ext cx="3524250" cy="3309620"/>
+          <a:off x="161290" y="805815"/>
+          <a:ext cx="4099560" cy="3847465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>46990</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>6483350</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="A diagram of the lakehouse architecture using Unity Catalog and delta tables."/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3" r:link="rId2"/>
+        <a:srcRect l="783" b="14452"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="107950" y="6543040"/>
+          <a:ext cx="6834505" cy="2261235"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>86360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3845560</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="227965" y="27715210"/>
+          <a:ext cx="4076700" cy="3181350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>34290</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>19685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3328035</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="312420" y="34538285"/>
+          <a:ext cx="3474720" cy="3618865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>65405</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>32385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2995295</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>140335</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="158115" y="42228135"/>
+          <a:ext cx="3296285" cy="3060700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>156210</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3426460</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>42545</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="248920" y="48006000"/>
+          <a:ext cx="3636645" cy="3484245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5302250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Diagram: Databricks architecture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:srcRect t="5907" r="5963" b="5887"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="1009650"/>
+          <a:ext cx="6178550" cy="2844800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1264,134 +3063,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:D46"/>
+  <dimension ref="B1:D209"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="4.31538461538462" style="13" customWidth="1"/>
-    <col min="2" max="2" width="2.96153846153846" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="9.23076923076923" style="14"/>
+    <col min="1" max="1" width="1.12307692307692" style="25" customWidth="1"/>
+    <col min="2" max="2" width="2.24615384615385" style="9" customWidth="1"/>
+    <col min="3" max="3" width="2.19230769230769" style="9" customWidth="1"/>
+    <col min="4" max="4" width="143.176923076923" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:4">
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:4">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="14" t="s">
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" ht="31" spans="2:4">
+      <c r="B3"/>
+      <c r="D3" s="26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
-      <c r="B4"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="14" t="s">
+    <row r="24" ht="31" spans="4:4">
+      <c r="D24" s="26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="14" t="s">
+    <row r="25" ht="31" spans="4:4">
+      <c r="D25" s="27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="14" t="s">
+    <row r="26" spans="4:4">
+      <c r="D26" s="27"/>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" s="27"/>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="15" t="s">
+    <row r="29" spans="4:4">
+      <c r="D29" s="26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="14" t="s">
+    <row r="30" spans="4:4">
+      <c r="D30" s="28" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="14" t="s">
+    <row r="32" spans="2:2">
+      <c r="B32"/>
+    </row>
+    <row r="44" ht="77.5" spans="4:4">
+      <c r="D44" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="14" t="s">
+    <row r="45" spans="4:4">
+      <c r="D45" s="26" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="3:3">
-      <c r="C30" s="14" t="s">
+    <row r="47" spans="3:3">
+      <c r="C47" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="3:3">
-      <c r="C31" s="18" t="s">
+    <row r="48" spans="4:4">
+      <c r="D48" s="26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="18" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="29" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="14" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="14" t="s">
+    <row r="52" spans="4:4">
+      <c r="D52" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="3:3">
-      <c r="C36" s="14" t="s">
+    <row r="54" ht="279" spans="4:4">
+      <c r="D54" s="27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="14" t="s">
+    <row r="55" spans="2:4">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55" s="28"/>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56" s="28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="14" t="s">
+    <row r="57" spans="2:4">
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57" s="28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="14" t="s">
+    <row r="58" spans="2:4">
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58" s="28"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59" s="28"/>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60"/>
+      <c r="C60" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="15" t="s">
+    <row r="61" spans="2:4">
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="3:3">
-      <c r="C43" s="14" t="s">
+    <row r="62" ht="17.5" spans="2:4">
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62" s="31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="15" t="s">
+    <row r="63" spans="2:4">
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="3:3">
-      <c r="C46" s="14" t="s">
+    <row r="64" spans="2:4">
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64" s="28" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="65" ht="62" spans="2:4">
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" ht="139.5" spans="2:4">
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68" s="28"/>
+    </row>
+    <row r="69" ht="31" spans="2:4">
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69" s="26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70" s="28"/>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71" s="28"/>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" ht="46.5" spans="2:4">
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75" s="28"/>
+    </row>
+    <row r="76" ht="155" spans="2:4">
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76" s="26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77" s="28"/>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78"/>
+      <c r="C78" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82" s="27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="2:4">
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83" s="27"/>
+    </row>
+    <row r="84" ht="156" customHeight="1" spans="2:4">
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85" s="28"/>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86" s="16"/>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87" s="28"/>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88" s="28"/>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89" s="28"/>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90" s="28"/>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91" s="28"/>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92" s="28"/>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93" s="28"/>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94" s="28"/>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95" s="28"/>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96" s="28"/>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97" s="28"/>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98" s="28"/>
+    </row>
+    <row r="103" spans="4:4">
+      <c r="D103" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4">
+      <c r="D105" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" ht="31" spans="4:4">
+      <c r="D106" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="108" ht="31" spans="4:4">
+      <c r="D108" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="110" ht="31" spans="4:4">
+      <c r="D110" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" ht="31" spans="4:4">
+      <c r="D112" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114" ht="31" spans="4:4">
+      <c r="D114" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="116" spans="4:4">
+      <c r="D116" s="16"/>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" s="27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="136" ht="31" spans="4:4">
+      <c r="D136" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="138" ht="31" spans="4:4">
+      <c r="D138" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140" ht="31" spans="4:4">
+      <c r="D140" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="142" ht="31" spans="4:4">
+      <c r="D142" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="144" ht="46.5" spans="4:4">
+      <c r="D144" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="146" ht="31" spans="4:4">
+      <c r="D146" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148"/>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" s="27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" ht="31" spans="4:4">
+      <c r="D165" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="167" ht="31" spans="4:4">
+      <c r="D167" s="26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="169" ht="31" spans="4:4">
+      <c r="D169" s="26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="171" ht="31" spans="4:4">
+      <c r="D171" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173"/>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="195" ht="46.5" spans="4:4">
+      <c r="D195" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="16"/>
+    </row>
+    <row r="197" ht="46.5" spans="4:4">
+      <c r="D197" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" s="16"/>
+    </row>
+    <row r="199" ht="31" spans="4:4">
+      <c r="D199" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" s="16"/>
+    </row>
+    <row r="201" ht="46.5" spans="4:4">
+      <c r="D201" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" s="16"/>
+    </row>
+    <row r="203" ht="31" spans="4:4">
+      <c r="D203" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="204" spans="4:4">
+      <c r="D204" s="16"/>
+    </row>
+    <row r="205" ht="62" spans="4:4">
+      <c r="D205" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="207" spans="4:4">
+      <c r="D207" s="27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="208" spans="4:4">
+      <c r="D208" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="209" ht="31" spans="4:4">
+      <c r="D209" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D62" r:id="rId2" display="Delta refers to technologies related to or in the Delta Lake open source project" tooltip="https://delta.io/"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -1399,47 +3607,1050 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="27.3307692307692" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="3"/>
+      <c r="D8" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="5"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="5"/>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="6"/>
+    </row>
+    <row r="57" spans="4:4">
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="7"/>
+    </row>
+    <row r="61" spans="3:6">
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+    </row>
+    <row r="62" spans="3:6">
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+    </row>
+    <row r="63" spans="3:6">
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+    </row>
+    <row r="64" spans="3:6">
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="F64" s="5"/>
+    </row>
+    <row r="65" spans="3:6">
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+    </row>
+    <row r="66" spans="3:6">
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="8"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="8"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="8"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="8"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="8"/>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="142" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:D176"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="4.53846153846154" style="13" customWidth="1"/>
-    <col min="2" max="2" width="3.13846153846154" style="14" customWidth="1"/>
-    <col min="3" max="3" width="3.47692307692308" style="14" customWidth="1"/>
-    <col min="4" max="4" width="17.7923076923077" style="14" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="14" customWidth="1"/>
-    <col min="6" max="6" width="23.4692307692308" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="9.23076923076923" style="14"/>
+    <col min="1" max="1" width="3" style="16" customWidth="1"/>
+    <col min="2" max="3" width="3.38461538461538" style="16" customWidth="1"/>
+    <col min="4" max="4" width="108.169230769231" style="19" customWidth="1"/>
+    <col min="5" max="16384" width="8.66923076923077" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:4">
-      <c r="D1" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="4:4">
-      <c r="D2" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="17">
-        <v>1</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="3:3">
+      <c r="C2" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" spans="3:3">
+      <c r="C8" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" spans="4:4">
+      <c r="D9" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" spans="3:3">
+      <c r="C10" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" spans="4:4">
+      <c r="D11" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" spans="4:4">
+      <c r="D12" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" spans="4:4">
+      <c r="D13" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" spans="4:4">
+      <c r="D14" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" spans="3:3">
+      <c r="C15" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="4:4">
+      <c r="D16" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" hidden="1" spans="4:4">
+      <c r="D17" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" hidden="1" spans="3:3">
+      <c r="C22" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" ht="31" hidden="1" spans="4:4">
+      <c r="D23" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" hidden="1" spans="4:4">
+      <c r="D24" s="19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" spans="3:3">
+      <c r="C25" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" ht="31" hidden="1" spans="4:4">
+      <c r="D26" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" hidden="1" spans="4:4">
+      <c r="D27" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" hidden="1" spans="3:3">
+      <c r="C28" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" ht="31" hidden="1" spans="4:4">
+      <c r="D29" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" hidden="1" spans="4:4">
+      <c r="D30" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" hidden="1" spans="3:3">
+      <c r="C31" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" hidden="1" spans="4:4">
+      <c r="D32" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" hidden="1" spans="4:4">
+      <c r="D33" s="19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" hidden="1" spans="3:3">
+      <c r="C34" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" hidden="1" spans="4:4">
+      <c r="D35" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" hidden="1" spans="3:3">
+      <c r="C36" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" ht="31" hidden="1" spans="4:4">
+      <c r="D37" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="4:4">
+      <c r="D38" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" hidden="1" spans="3:3">
+      <c r="C39" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" ht="46.5" hidden="1" spans="4:4">
+      <c r="D40" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" hidden="1" spans="4:4">
+      <c r="D41" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" hidden="1" spans="4:4">
+      <c r="D42" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" spans="3:3">
+      <c r="C43" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" ht="14" hidden="1" customHeight="1" spans="4:4">
+      <c r="D44" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" hidden="1" spans="4:4">
+      <c r="D45" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" spans="4:4">
+      <c r="D46" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="4:4">
+      <c r="D47" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="3:3">
+      <c r="C48" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" ht="46.5" hidden="1" spans="4:4">
+      <c r="D49" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="4:4">
+      <c r="D50" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="3:3">
+      <c r="C51" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" ht="31" hidden="1" spans="4:4">
+      <c r="D52" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="4:4">
+      <c r="D53" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" spans="4:4">
+      <c r="D54" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" spans="3:3">
+      <c r="C57" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" spans="4:4">
+      <c r="D58" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" spans="3:4">
+      <c r="C59" s="21"/>
+      <c r="D59" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" ht="31" hidden="1" spans="3:4">
+      <c r="C60" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" ht="31" hidden="1" spans="3:4">
+      <c r="C61" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" spans="3:4">
+      <c r="C62" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="22"/>
+    </row>
+    <row r="63" ht="31" hidden="1" spans="3:4">
+      <c r="C63" s="21"/>
+      <c r="D63" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" spans="3:4">
+      <c r="C64" s="21"/>
+      <c r="D64" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" ht="33" hidden="1" customHeight="1" spans="3:4">
+      <c r="C65" s="21"/>
+      <c r="D65" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" spans="3:4">
+      <c r="C66" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D66" s="22"/>
+    </row>
+    <row r="67" hidden="1" spans="3:4">
+      <c r="C67" s="21"/>
+      <c r="D67" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" ht="31" hidden="1" spans="3:4">
+      <c r="C68" s="21"/>
+      <c r="D68" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" ht="46.5" hidden="1" spans="3:4">
+      <c r="C69" s="21"/>
+      <c r="D69" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" spans="3:4">
+      <c r="C70" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D70" s="22"/>
+    </row>
+    <row r="71" ht="31" hidden="1" spans="3:4">
+      <c r="C71" s="21"/>
+      <c r="D71" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" spans="3:4">
+      <c r="C72" s="21"/>
+      <c r="D72" s="22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="3:4">
+      <c r="C73" s="21"/>
+      <c r="D73" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" spans="3:4">
+      <c r="C74" s="21"/>
+      <c r="D74" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" spans="3:4">
+      <c r="C75" s="21"/>
+      <c r="D75" s="22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" spans="3:4">
+      <c r="C76" s="21"/>
+      <c r="D76" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" spans="3:4">
+      <c r="C77" s="21"/>
+      <c r="D77" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="78" hidden="1" spans="3:4">
+      <c r="C78" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="22"/>
+    </row>
+    <row r="79" ht="31" hidden="1" spans="3:4">
+      <c r="C79" s="21"/>
+      <c r="D79" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="80" hidden="1" spans="4:4">
+      <c r="D80" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" ht="31" hidden="1" spans="4:4">
+      <c r="D81" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="82" hidden="1" spans="3:3">
+      <c r="C82" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="83" ht="31" hidden="1" spans="4:4">
+      <c r="D83" s="19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" spans="3:3">
+      <c r="C87" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="88" ht="31" hidden="1" spans="4:4">
+      <c r="D88" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="3:3">
+      <c r="C89" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" ht="31" hidden="1" spans="4:4">
+      <c r="D90" s="19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="91" hidden="1" spans="4:4">
+      <c r="D91" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" hidden="1" spans="3:3">
+      <c r="C92" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" ht="31" hidden="1" spans="4:4">
+      <c r="D93" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="94" hidden="1" spans="4:4">
+      <c r="D94" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="95" hidden="1" spans="3:3">
+      <c r="C95" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="96" ht="31" hidden="1" spans="4:4">
+      <c r="D96" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="97" hidden="1" spans="4:4">
+      <c r="D97" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="100" ht="31" spans="4:4">
+      <c r="D100" s="19" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="3:3">
+      <c r="C101" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="102" ht="31" hidden="1" spans="4:4">
+      <c r="D102" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="103" hidden="1" spans="4:4">
+      <c r="D103" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="104" hidden="1" spans="3:3">
+      <c r="C104" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" ht="62" hidden="1" spans="4:4">
+      <c r="D105" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" hidden="1" spans="4:4">
+      <c r="D106" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" hidden="1" spans="3:3">
+      <c r="C107" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108" hidden="1" spans="4:4">
+      <c r="D108" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109" hidden="1" spans="4:4">
+      <c r="D109" s="19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" hidden="1" spans="4:4">
+      <c r="D110" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="111" hidden="1" spans="4:4">
+      <c r="D111" s="19" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="112" ht="31" hidden="1" spans="4:4">
+      <c r="D112" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" hidden="1" spans="4:4">
+      <c r="D113" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="114" hidden="1" spans="4:4">
+      <c r="D114" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115" hidden="1" spans="4:4">
+      <c r="D115" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="116" hidden="1" spans="4:4">
+      <c r="D116" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="117" hidden="1" spans="3:3">
+      <c r="C117" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" ht="31" hidden="1" spans="4:4">
+      <c r="D118" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="119" hidden="1" spans="4:4">
+      <c r="D119" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="120" ht="31" hidden="1" spans="4:4">
+      <c r="D120" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="121" hidden="1" spans="3:3">
+      <c r="C121" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="122" hidden="1" spans="4:4">
+      <c r="D122" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="123" ht="31" hidden="1" spans="4:4">
+      <c r="D123" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="124" hidden="1" spans="4:4">
+      <c r="D124" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="125" hidden="1" spans="4:4">
+      <c r="D125" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="126" hidden="1" spans="4:4">
+      <c r="D126" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="127" hidden="1" spans="4:4">
+      <c r="D127" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="128" ht="31" hidden="1" spans="4:4">
+      <c r="D128" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="129" hidden="1" spans="3:3">
+      <c r="C129" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="130" ht="31" hidden="1" spans="4:4">
+      <c r="D130" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" hidden="1" spans="4:4">
+      <c r="D131" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="132" hidden="1" spans="3:3">
+      <c r="C132" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="133" ht="46.5" hidden="1" spans="4:4">
+      <c r="D133" s="19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="134" hidden="1" spans="4:4">
+      <c r="D134" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="137" ht="31" spans="4:4">
+      <c r="D137" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="139" hidden="1" spans="3:3">
+      <c r="C139" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="140" ht="31" hidden="1" spans="4:4">
+      <c r="D140" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="141" hidden="1" spans="4:4">
+      <c r="D141" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="142" hidden="1" spans="3:3">
+      <c r="C142" s="16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="143" ht="31" hidden="1" spans="4:4">
+      <c r="D143" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="144" hidden="1" spans="4:4">
+      <c r="D144" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="145" hidden="1" spans="3:3">
+      <c r="C145" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" spans="4:4">
+      <c r="D146" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="147" hidden="1" spans="4:4">
+      <c r="D147" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="148" hidden="1" spans="3:3">
+      <c r="C148" s="16" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="149" ht="31" hidden="1" spans="4:4">
+      <c r="D149" s="19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="150" hidden="1" spans="4:4">
+      <c r="D150" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="151" hidden="1" spans="4:4">
+      <c r="D151" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3">
+      <c r="C157" s="16" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3">
+      <c r="C158" s="16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3">
+      <c r="C159" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3">
+      <c r="C160" s="16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3">
+      <c r="C161" s="16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="162" ht="31" spans="4:4">
+      <c r="D162" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3">
+      <c r="C163" s="16" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3">
+      <c r="C165" s="16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3">
+      <c r="C166" s="16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3">
+      <c r="C167" s="16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="170" spans="3:3">
+      <c r="C170" s="16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="15"/>
+      <c r="B172" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="15"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="15"/>
+      <c r="B174" s="15"/>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="15"/>
+      <c r="B175" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="15"/>
+      <c r="B176" s="15"/>
+      <c r="C176" s="16" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1447,215 +4658,581 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H88"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:D87"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="27.3307692307692" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="5" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="5" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="5" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="5"/>
+    <col min="1" max="3" width="4" style="9" customWidth="1"/>
+    <col min="4" max="4" width="130.461538461538" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="3:3">
-      <c r="C3" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="4:4">
-      <c r="D5" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="4:4">
-      <c r="D6" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="4:4">
-      <c r="D7" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="7"/>
-      <c r="D8" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="8"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="9"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="9"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="9"/>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="9"/>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="9"/>
+    <row r="1" spans="1:3">
+      <c r="A1" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" ht="31" spans="4:4">
+      <c r="D31" s="10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" ht="31" spans="4:4">
+      <c r="D36" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="17"/>
+      <c r="D39" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" ht="31" spans="4:4">
+      <c r="D40" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" ht="31" spans="4:4">
+      <c r="D42" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="17" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="51" ht="46.5" spans="4:4">
+      <c r="D51" s="10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" ht="62" spans="4:4">
+      <c r="D54" s="10" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="10"/>
-    </row>
-    <row r="57" spans="4:4">
-      <c r="D57" s="10"/>
-    </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="11"/>
-    </row>
-    <row r="61" spans="3:6">
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-    </row>
-    <row r="62" spans="3:6">
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-    </row>
-    <row r="63" spans="3:6">
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-    </row>
-    <row r="64" spans="3:6">
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="F64" s="9"/>
-    </row>
-    <row r="65" spans="3:6">
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-    </row>
-    <row r="66" spans="3:6">
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="12"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="12"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="12"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="12"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="12"/>
-    </row>
-    <row r="88" spans="4:4">
-      <c r="D88" s="10"/>
+      <c r="D56" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" ht="46.5" spans="4:4">
+      <c r="D57" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" ht="31" spans="4:4">
+      <c r="D59" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4">
+      <c r="D60" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="17" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" s="17"/>
+      <c r="C63" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" ht="46.5" spans="2:4">
+      <c r="B64" s="17"/>
+      <c r="D64" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="17"/>
+      <c r="D65" s="10" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="17"/>
+      <c r="D66" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="17"/>
+      <c r="D67" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="17"/>
+      <c r="D68" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="17"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3">
+      <c r="C71" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4">
+      <c r="D72" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4">
+      <c r="D73" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4">
+      <c r="D74" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4">
+      <c r="D77" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4">
+      <c r="D78" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="79" ht="31" spans="4:4">
+      <c r="D79" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4">
+      <c r="D81" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4">
+      <c r="D82" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="87" ht="31" spans="4:4">
+      <c r="D87" s="10" t="s">
+        <v>297</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="142" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:D237"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="25.2538461538462" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="2" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="2"/>
+    <col min="1" max="3" width="3" style="11" customWidth="1"/>
+    <col min="4" max="4" width="156.923076923077" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:7">
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>31</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="4:4">
+      <c r="D2" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" ht="46.5" spans="4:4">
+      <c r="D3" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" ht="31" spans="3:4">
+      <c r="C8" s="13"/>
+      <c r="D8" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" ht="93" spans="3:4">
+      <c r="C9" s="13"/>
+      <c r="D9" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" ht="77.5" spans="3:4">
+      <c r="C10" s="13"/>
+      <c r="D10" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="13"/>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" ht="31" spans="3:4">
+      <c r="C13" s="13"/>
+      <c r="D13" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" ht="93" spans="4:4">
+      <c r="D14" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" ht="77.5" spans="4:4">
+      <c r="D15" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" ht="46.5" spans="4:4">
+      <c r="D17" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="B230" s="13"/>
+      <c r="C230" s="13"/>
+      <c r="D230" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="232" ht="31" spans="1:4">
+      <c r="A232" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B232" s="12"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="233" ht="46.5" spans="1:4">
+      <c r="A233" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B233" s="12"/>
+      <c r="C233" s="12"/>
+      <c r="D233" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B235" s="13"/>
+      <c r="C235" s="13"/>
+      <c r="D235" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D236" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D237" s="12" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A232:C232"/>
+    <mergeCell ref="A233:C233"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="142" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1663,49 +5240,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H5"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="17.2538461538462" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.66923076923077" style="2"/>
-    <col min="3" max="3" width="5.66923076923077" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.4692307692308" style="2" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="2"/>
-  </cols>
+  <dimension ref="B3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="14.75"/>
-    <row r="4" ht="14.75" spans="4:4">
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" ht="14.75" spans="4:4">
-      <c r="D5" s="4"/>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>330</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="142" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1714,10 +5258,93 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:D15"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="16384" width="8.66923076923077" style="1"/>
+    <col min="1" max="1" width="2.76923076923077" style="9" customWidth="1"/>
+    <col min="2" max="2" width="2.61538461538462" style="9" customWidth="1"/>
+    <col min="3" max="3" width="3.23076923076923" style="9" customWidth="1"/>
+    <col min="4" max="4" width="153.615384615385" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="9"/>
   </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" spans="3:3">
+      <c r="C2" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="5" ht="31" spans="4:4">
+      <c r="D5" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" ht="31" spans="4:4">
+      <c r="D7" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9" ht="31" spans="4:4">
+      <c r="D9" s="10" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" ht="31" spans="4:4">
+      <c r="D13" s="10" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1" spans="4:4">
+      <c r="D14" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/p/ds_25/databricks/topic-list_DtBrk.xlsx
+++ b/p/ds_25/databricks/topic-list_DtBrk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="698" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="what-how" sheetId="21" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="OLTP" sheetId="31" r:id="rId8"/>
     <sheet name="ML" sheetId="30" r:id="rId9"/>
     <sheet name="core" sheetId="2" r:id="rId10"/>
+    <sheet name="walk" sheetId="33" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="405">
   <si>
     <t>Azure Databrick</t>
   </si>
@@ -538,6 +539,39 @@
     <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/</t>
   </si>
   <si>
+    <t>4 key functional areas of data governance</t>
+  </si>
+  <si>
+    <t>Data Access Control</t>
+  </si>
+  <si>
+    <t>Data Access Audit</t>
+  </si>
+  <si>
+    <t>Data Lineage</t>
+  </si>
+  <si>
+    <t>Data Discovery</t>
+  </si>
+  <si>
+    <t>Requirements: Premium databricks workspace, Workspace and Metastore should be in same region, Premium blob storage account as root container</t>
+  </si>
+  <si>
+    <t>Metastore</t>
+  </si>
+  <si>
+    <t>Unity Catalog provides an account-level metastore that registers metadata about data, AI, and permissions about catalogs, schemas, and tables.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/#metastore</t>
+  </si>
+  <si>
+    <t>Azure Databricks provides a legacy Hive metastore for customers that have not adopted Unity Catalog</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/table-acls/</t>
+  </si>
+  <si>
     <t>Catalog</t>
   </si>
   <si>
@@ -584,21 +618,6 @@
   </si>
   <si>
     <t>By default, all tables created in Azure Databricks are Delta tables. Delta tables are based on the Delta Lake open source project, a framework for high-performance ACID table storage over cloud object stores. A Delta table stores data as a directory of files on cloud object storage and registers table metadata to the metastore within a catalog and schema.</t>
-  </si>
-  <si>
-    <t>Metastore</t>
-  </si>
-  <si>
-    <t>Unity Catalog provides an account-level metastore that registers metadata about data, AI, and permissions about catalogs, schemas, and tables.</t>
-  </si>
-  <si>
-    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/unity-catalog/#metastore</t>
-  </si>
-  <si>
-    <t>Azure Databricks provides a legacy Hive metastore for customers that have not adopted Unity Catalog</t>
-  </si>
-  <si>
-    <t>https://learn.microsoft.com/en-us/azure/databricks/data-governance/table-acls/</t>
   </si>
   <si>
     <t>Catalog Explorer</t>
@@ -1534,6 +1553,56 @@
     <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/procedural-vs-declarative#when-to-choose-procedural-or-declarative-processing</t>
   </si>
   <si>
+    <t>Batch vs. streaming data processing</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/batch-vs-streaming</t>
+  </si>
+  <si>
+    <t>Tables and views</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/data-engineering/tables-views</t>
+  </si>
+  <si>
+    <t>What is change data capture</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/dlt/what-is-change-data-capture</t>
+  </si>
+  <si>
+    <t>Work with joins</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/transform/join</t>
+  </si>
+  <si>
+    <t>Aggregate data</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/transform/aggregation</t>
+  </si>
+  <si>
+    <t>Lakeflow Jobs</t>
+  </si>
+  <si>
+    <t>Tutorial</t>
+  </si>
+  <si>
+    <t>Use a py package</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/jobs/how-to/use-python-wheels-in-workflows</t>
+  </si>
+  <si>
+    <t>Step 1: Create a local directory for the example
+Step 2: Create the example Python script
+Step 3: Create a metadata file for the package
+Step 4: Create the Python wheel file
+Step 5. Create a job to run the Python wheel file
+Step 6: Run the job and view the job run details</t>
+  </si>
+  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -1576,6 +1645,39 @@
     <t>https://learn.microsoft.com/en-us/azure/databricks/spark/</t>
   </si>
   <si>
+    <t>CI/CD</t>
+  </si>
+  <si>
+    <t>Databricks Assets Bundles</t>
+  </si>
+  <si>
+    <t>Develop bundles</t>
+  </si>
+  <si>
+    <t>Lifecycle of a bundle</t>
+  </si>
+  <si>
+    <t>To understand how to effectively use bundles, you need to understand the basic lifecycle of a bundle:
+The bundle skeleton is created based on a project.
+The bundle project is developed locally. A bundle contains configuration files that define infrastructure and workspace settings such as deployment targets, settings for Databricks resources such as jobs and pipelines, as well as source files and other artifacts.
+The bundle project is validated. Validation verifies the settings and resource definitions in the bundle configuration against the corresponding object schemas to ensure the bundle is deployable to Databricks.
+The bundle is deployed to a target workspace. Most commonly a bundle is first deployed to a user's personal dev workspace for testing. Once testing of the bundle is finished, the bundle can be deployed to staging, then production targets.
+Workflow resources defined in the deployed bundle can be run. For example, you can run a job.
+If the bundle is no longer being used, it can be permanently destroyed.
+You use the Databricks CLI bundle commands to create, validate, deploy, run, and destroy bundles, as described in the following sections.</t>
+  </si>
+  <si>
+    <t>Step 1: Create a bundle
+Step 2: Populate the bundle configuration files
+Step 3: Validate the bundle configuration files
+Step 4: Deploy the bundle
+Step 5: Run the bundle
+Step 6: Destroy the bundle</t>
+  </si>
+  <si>
+    <t>Bundle with job tutorial</t>
+  </si>
+  <si>
     <t>OLTP Database</t>
   </si>
   <si>
@@ -1637,6 +1739,81 @@
   </si>
   <si>
     <t>Forecasting</t>
+  </si>
+  <si>
+    <t>Databrick Walkthrough</t>
+  </si>
+  <si>
+    <t>Get region which have serverless sql warehouse and near to your location</t>
+  </si>
+  <si>
+    <t>Resource group</t>
+  </si>
+  <si>
+    <t>to hold all our resources</t>
+  </si>
+  <si>
+    <t>// one more resource group will also get created after databrick workspace provisioning for compute  resources</t>
+  </si>
+  <si>
+    <t>Create Databrick</t>
+  </si>
+  <si>
+    <t>Select your resource group</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>Pricing tier</t>
+  </si>
+  <si>
+    <t>Networking -&gt; with secure cluster connectivity : No</t>
+  </si>
+  <si>
+    <t>networking -&gt; virtual network : No</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>Once it provisioning get complete, use "Go to resource"</t>
+  </si>
+  <si>
+    <t>Launch workspace</t>
+  </si>
+  <si>
+    <t>Use to keep all your queries and data organised</t>
+  </si>
+  <si>
+    <t>it also have shared folder</t>
+  </si>
+  <si>
+    <t>items available to add: folder, query, alert, dashboard, notebook, library, mlFlow, File</t>
+  </si>
+  <si>
+    <t>Repos can also be added here in workspace</t>
+  </si>
+  <si>
+    <t>Data Explorer</t>
+  </si>
+  <si>
+    <t>Manage various data sources</t>
+  </si>
+  <si>
+    <t>Enabling Unity Catalog</t>
+  </si>
+  <si>
+    <t>Create Storage account and link to your resource group with region</t>
+  </si>
+  <si>
+    <t>Account type: Block blob</t>
+  </si>
+  <si>
+    <t>Redundancy: Locally-redundant storage</t>
+  </si>
+  <si>
+    <t>Enable Hierarchical namespace: yes</t>
   </si>
 </sst>
 </file>
@@ -1651,6 +1828,14 @@
   </numFmts>
   <fonts count="33">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1686,14 +1871,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2347,22 +2524,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2371,11 +2552,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2384,22 +2568,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2418,6 +2599,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2742,6 +2926,53 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>40640</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>32385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5266055</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>120015</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40640" y="2197735"/>
+          <a:ext cx="6031865" cy="1662430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
@@ -2776,6 +3007,53 @@
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>58420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6336665</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="50800" y="5963920"/>
+          <a:ext cx="7200265" cy="2040255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -3066,58 +3344,58 @@
   <dimension ref="B1:D209"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="1.12307692307692" style="25" customWidth="1"/>
-    <col min="2" max="2" width="2.24615384615385" style="9" customWidth="1"/>
-    <col min="3" max="3" width="2.19230769230769" style="9" customWidth="1"/>
-    <col min="4" max="4" width="143.176923076923" style="26" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="9"/>
+    <col min="1" max="1" width="1.12307692307692" style="27" customWidth="1"/>
+    <col min="2" max="2" width="2.24615384615385" style="10" customWidth="1"/>
+    <col min="3" max="3" width="2.19230769230769" style="10" customWidth="1"/>
+    <col min="4" max="4" width="143.176923076923" style="28" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:4">
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="29" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:4">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="27"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" ht="31" spans="2:4">
       <c r="B3"/>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="28" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="24" ht="31" spans="4:4">
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="28" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="25" ht="31" spans="4:4">
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="29" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="4:4">
-      <c r="D26" s="27"/>
+      <c r="D26" s="29"/>
     </row>
     <row r="27" spans="4:4">
-      <c r="D27" s="27"/>
+      <c r="D27" s="29"/>
     </row>
     <row r="28" spans="3:3">
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="4:4">
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="4:4">
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="30" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3125,373 +3403,373 @@
       <c r="B32"/>
     </row>
     <row r="44" ht="77.5" spans="4:4">
-      <c r="D44" s="26" t="s">
+      <c r="D44" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="4:4">
-      <c r="D45" s="26" t="s">
+      <c r="D45" s="28" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="47" spans="3:3">
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="4:4">
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="4:4">
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="31" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="26" t="s">
+      <c r="D51" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="52" spans="4:4">
-      <c r="D52" s="26" t="s">
+      <c r="D52" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="54" ht="279" spans="4:4">
-      <c r="D54" s="27" t="s">
+      <c r="D54" s="29" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="B55"/>
       <c r="C55"/>
-      <c r="D55" s="28"/>
+      <c r="D55" s="30"/>
     </row>
     <row r="56" spans="2:4">
       <c r="B56"/>
       <c r="C56"/>
-      <c r="D56" s="28" t="s">
+      <c r="D56" s="30" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57"/>
       <c r="C57"/>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="30" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="B58"/>
       <c r="C58"/>
-      <c r="D58" s="28"/>
+      <c r="D58" s="30"/>
     </row>
     <row r="59" spans="2:4">
       <c r="B59"/>
       <c r="C59"/>
-      <c r="D59" s="28"/>
+      <c r="D59" s="30"/>
     </row>
     <row r="60" spans="2:3">
       <c r="B60"/>
-      <c r="C60" s="30" t="s">
+      <c r="C60" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="2:4">
       <c r="B61"/>
       <c r="C61"/>
-      <c r="D61" s="28" t="s">
+      <c r="D61" s="30" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="62" ht="17.5" spans="2:4">
       <c r="B62"/>
       <c r="C62"/>
-      <c r="D62" s="31" t="s">
+      <c r="D62" s="33" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="63" spans="2:4">
       <c r="B63"/>
       <c r="C63"/>
-      <c r="D63" s="28" t="s">
+      <c r="D63" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="64" spans="2:4">
       <c r="B64"/>
       <c r="C64"/>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="30" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="65" ht="62" spans="2:4">
       <c r="B65"/>
       <c r="C65"/>
-      <c r="D65" s="26" t="s">
+      <c r="D65" s="28" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="B66"/>
       <c r="C66"/>
-      <c r="D66" s="28"/>
+      <c r="D66" s="30"/>
     </row>
     <row r="67" ht="139.5" spans="2:4">
       <c r="B67"/>
       <c r="C67"/>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="29" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="B68"/>
       <c r="C68"/>
-      <c r="D68" s="28"/>
+      <c r="D68" s="30"/>
     </row>
     <row r="69" ht="31" spans="2:4">
       <c r="B69"/>
       <c r="C69"/>
-      <c r="D69" s="26" t="s">
+      <c r="D69" s="28" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="B70"/>
       <c r="C70"/>
-      <c r="D70" s="28"/>
+      <c r="D70" s="30"/>
     </row>
     <row r="71" spans="2:4">
       <c r="B71"/>
       <c r="C71"/>
-      <c r="D71" s="28"/>
+      <c r="D71" s="30"/>
     </row>
     <row r="72" spans="2:4">
       <c r="B72"/>
       <c r="C72"/>
-      <c r="D72" s="28" t="s">
+      <c r="D72" s="30" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="B73"/>
       <c r="C73"/>
-      <c r="D73" s="30" t="s">
+      <c r="D73" s="32" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="74" ht="46.5" spans="2:4">
       <c r="B74"/>
       <c r="C74"/>
-      <c r="D74" s="26" t="s">
+      <c r="D74" s="28" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="75" spans="2:4">
       <c r="B75"/>
       <c r="C75"/>
-      <c r="D75" s="28"/>
+      <c r="D75" s="30"/>
     </row>
     <row r="76" ht="155" spans="2:4">
       <c r="B76"/>
       <c r="C76"/>
-      <c r="D76" s="26" t="s">
+      <c r="D76" s="28" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77"/>
       <c r="C77"/>
-      <c r="D77" s="28"/>
+      <c r="D77" s="30"/>
     </row>
     <row r="78" spans="2:3">
       <c r="B78"/>
-      <c r="C78" s="30" t="s">
+      <c r="C78" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="79" spans="2:4">
       <c r="B79"/>
       <c r="C79"/>
-      <c r="D79" s="28" t="s">
+      <c r="D79" s="30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="80" spans="2:4">
       <c r="B80"/>
       <c r="C80"/>
-      <c r="D80" s="28" t="s">
+      <c r="D80" s="30" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="81" spans="2:4">
       <c r="B81"/>
       <c r="C81"/>
-      <c r="D81" s="27" t="s">
+      <c r="D81" s="29" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="B82"/>
       <c r="C82"/>
-      <c r="D82" s="27" t="s">
+      <c r="D82" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" spans="2:4">
       <c r="B83"/>
       <c r="C83"/>
-      <c r="D83" s="27"/>
+      <c r="D83" s="29"/>
     </row>
     <row r="84" ht="156" customHeight="1" spans="2:4">
       <c r="B84"/>
       <c r="C84"/>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="B85"/>
       <c r="C85"/>
-      <c r="D85" s="28"/>
+      <c r="D85" s="30"/>
     </row>
     <row r="86" spans="2:4">
       <c r="B86"/>
       <c r="C86"/>
-      <c r="D86" s="16"/>
+      <c r="D86" s="19"/>
     </row>
     <row r="87" spans="2:4">
       <c r="B87"/>
       <c r="C87"/>
-      <c r="D87" s="28"/>
+      <c r="D87" s="30"/>
     </row>
     <row r="88" spans="2:4">
       <c r="B88"/>
       <c r="C88"/>
-      <c r="D88" s="28"/>
+      <c r="D88" s="30"/>
     </row>
     <row r="89" spans="2:4">
       <c r="B89"/>
       <c r="C89"/>
-      <c r="D89" s="28"/>
+      <c r="D89" s="30"/>
     </row>
     <row r="90" spans="2:4">
       <c r="B90"/>
       <c r="C90"/>
-      <c r="D90" s="28"/>
+      <c r="D90" s="30"/>
     </row>
     <row r="91" spans="2:4">
       <c r="B91"/>
       <c r="C91"/>
-      <c r="D91" s="28"/>
+      <c r="D91" s="30"/>
     </row>
     <row r="92" spans="2:4">
       <c r="B92"/>
       <c r="C92"/>
-      <c r="D92" s="28"/>
+      <c r="D92" s="30"/>
     </row>
     <row r="93" spans="2:4">
       <c r="B93"/>
       <c r="C93"/>
-      <c r="D93" s="28"/>
+      <c r="D93" s="30"/>
     </row>
     <row r="94" spans="2:4">
       <c r="B94"/>
       <c r="C94"/>
-      <c r="D94" s="28"/>
+      <c r="D94" s="30"/>
     </row>
     <row r="95" spans="2:4">
       <c r="B95"/>
       <c r="C95"/>
-      <c r="D95" s="28"/>
+      <c r="D95" s="30"/>
     </row>
     <row r="96" spans="2:4">
       <c r="B96"/>
       <c r="C96"/>
-      <c r="D96" s="28"/>
+      <c r="D96" s="30"/>
     </row>
     <row r="97" spans="2:4">
       <c r="B97"/>
       <c r="C97"/>
-      <c r="D97" s="28"/>
+      <c r="D97" s="30"/>
     </row>
     <row r="98" spans="2:4">
       <c r="B98"/>
       <c r="C98"/>
-      <c r="D98" s="28"/>
+      <c r="D98" s="30"/>
     </row>
     <row r="103" spans="4:4">
-      <c r="D103" s="26" t="s">
+      <c r="D103" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="105" spans="4:4">
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="106" ht="31" spans="4:4">
-      <c r="D106" s="26" t="s">
+      <c r="D106" s="28" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="108" ht="31" spans="4:4">
-      <c r="D108" s="26" t="s">
+      <c r="D108" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="110" ht="31" spans="4:4">
-      <c r="D110" s="26" t="s">
+      <c r="D110" s="28" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="112" ht="31" spans="4:4">
-      <c r="D112" s="26" t="s">
+      <c r="D112" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="114" ht="31" spans="4:4">
-      <c r="D114" s="26" t="s">
+      <c r="D114" s="28" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="116" spans="4:4">
-      <c r="D116" s="16"/>
+      <c r="D116" s="19"/>
     </row>
     <row r="135" spans="4:4">
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" ht="31" spans="4:4">
-      <c r="D136" s="26" t="s">
+      <c r="D136" s="28" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="138" ht="31" spans="4:4">
-      <c r="D138" s="26" t="s">
+      <c r="D138" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="140" ht="31" spans="4:4">
-      <c r="D140" s="26" t="s">
+      <c r="D140" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="142" ht="31" spans="4:4">
-      <c r="D142" s="26" t="s">
+      <c r="D142" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="144" ht="46.5" spans="4:4">
-      <c r="D144" s="26" t="s">
+      <c r="D144" s="28" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="146" ht="31" spans="4:4">
-      <c r="D146" s="26" t="s">
+      <c r="D146" s="28" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3499,27 +3777,27 @@
       <c r="B148"/>
     </row>
     <row r="164" spans="4:4">
-      <c r="D164" s="27" t="s">
+      <c r="D164" s="29" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="165" ht="31" spans="4:4">
-      <c r="D165" s="26" t="s">
+      <c r="D165" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="167" ht="31" spans="4:4">
-      <c r="D167" s="26" t="s">
+      <c r="D167" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="169" ht="31" spans="4:4">
-      <c r="D169" s="26" t="s">
+      <c r="D169" s="28" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="171" ht="31" spans="4:4">
-      <c r="D171" s="26" t="s">
+      <c r="D171" s="28" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3527,72 +3805,72 @@
       <c r="B173"/>
     </row>
     <row r="192" spans="4:4">
-      <c r="D192" s="27" t="s">
+      <c r="D192" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="193" spans="4:4">
-      <c r="D193" s="26" t="s">
+      <c r="D193" s="28" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="195" ht="46.5" spans="4:4">
-      <c r="D195" s="19" t="s">
+      <c r="D195" s="34" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="196" spans="4:4">
-      <c r="D196" s="16"/>
+      <c r="D196" s="19"/>
     </row>
     <row r="197" ht="46.5" spans="4:4">
-      <c r="D197" s="19" t="s">
+      <c r="D197" s="34" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="198" spans="4:4">
-      <c r="D198" s="16"/>
+      <c r="D198" s="19"/>
     </row>
     <row r="199" ht="31" spans="4:4">
-      <c r="D199" s="19" t="s">
+      <c r="D199" s="34" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="200" spans="4:4">
-      <c r="D200" s="16"/>
+      <c r="D200" s="19"/>
     </row>
     <row r="201" ht="46.5" spans="4:4">
-      <c r="D201" s="19" t="s">
+      <c r="D201" s="34" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="202" spans="4:4">
-      <c r="D202" s="16"/>
+      <c r="D202" s="19"/>
     </row>
     <row r="203" ht="31" spans="4:4">
-      <c r="D203" s="19" t="s">
+      <c r="D203" s="34" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="204" spans="4:4">
-      <c r="D204" s="16"/>
+      <c r="D204" s="19"/>
     </row>
     <row r="205" ht="62" spans="4:4">
-      <c r="D205" s="19" t="s">
+      <c r="D205" s="34" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="207" spans="4:4">
-      <c r="D207" s="27" t="s">
+      <c r="D207" s="29" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="208" spans="4:4">
-      <c r="D208" s="26" t="s">
+      <c r="D208" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="209" ht="31" spans="4:4">
-      <c r="D209" s="26" t="s">
+      <c r="D209" s="28" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3613,162 +3891,162 @@
   <dimension ref="A1:H88"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="27.3307692307692" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="27.3307692307692" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="2" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.6692307692308" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="2" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="1" t="s">
-        <v>340</v>
+      <c r="B1" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>346</v>
+      <c r="A2" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="1" t="s">
-        <v>347</v>
+      <c r="C3" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="1" t="s">
-        <v>348</v>
+      <c r="D5" s="2" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="4:4">
-      <c r="D6" s="1" t="s">
-        <v>349</v>
+      <c r="D6" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="4:4">
-      <c r="D7" s="1" t="s">
-        <v>350</v>
+      <c r="D7" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="3"/>
-      <c r="D8" s="1" t="s">
-        <v>351</v>
+      <c r="B8" s="4"/>
+      <c r="D8" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5"/>
+      <c r="A33" s="6"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="5"/>
+      <c r="A40" s="6"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="5"/>
+      <c r="A41" s="6"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="5"/>
+      <c r="A43" s="6"/>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="6"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="4:4">
-      <c r="D57" s="6"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="4:4">
-      <c r="D58" s="7"/>
+      <c r="D58" s="8"/>
     </row>
     <row r="61" spans="3:6">
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
     </row>
     <row r="62" spans="3:6">
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
     </row>
     <row r="63" spans="3:6">
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
     </row>
     <row r="64" spans="3:6">
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="F64" s="6"/>
     </row>
     <row r="65" spans="3:6">
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
     </row>
     <row r="66" spans="3:6">
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="8"/>
+      <c r="B80" s="9"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="8"/>
+      <c r="B81" s="9"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="8"/>
+      <c r="B82" s="9"/>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="8"/>
+      <c r="B83" s="9"/>
     </row>
     <row r="84" spans="2:2">
-      <c r="B84" s="8"/>
+      <c r="B84" s="9"/>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="6"/>
+      <c r="D88" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3777,881 +4055,1092 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="4" width="2.76923076923077" style="1" customWidth="1"/>
+    <col min="5" max="5" width="99.6384615384615" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="5:5">
+      <c r="E4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="5:5">
+      <c r="E7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8" spans="5:5">
+      <c r="E8" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="5:5">
+      <c r="E12" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5">
+      <c r="E13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="5:5">
+      <c r="E15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="16" spans="5:5">
+      <c r="E16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" t="s">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="3" style="16" customWidth="1"/>
-    <col min="2" max="3" width="3.38461538461538" style="16" customWidth="1"/>
-    <col min="4" max="4" width="108.169230769231" style="19" customWidth="1"/>
-    <col min="5" max="16384" width="8.66923076923077" style="16"/>
+    <col min="1" max="1" width="3" style="19" customWidth="1"/>
+    <col min="2" max="3" width="3.38461538461538" style="19" customWidth="1"/>
+    <col min="4" max="4" width="108.169230769231" style="22" customWidth="1"/>
+    <col min="5" max="16384" width="8.66923076923077" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="3:3">
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="19" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" hidden="1" spans="3:3">
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="19" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="4:4">
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" hidden="1" spans="3:3">
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="19" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" hidden="1" spans="4:4">
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" hidden="1" spans="4:4">
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="4:4">
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="4:4">
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="3:3">
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="19" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="4:4">
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="22" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="4:4">
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="22" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="20" spans="4:4">
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="22" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" spans="4:4">
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="22" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="3:3">
-      <c r="C22" s="16" t="s">
+    <row r="31" spans="3:3">
+      <c r="C31" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" ht="31" hidden="1" spans="4:4">
-      <c r="D23" s="19" t="s">
+    <row r="32" ht="31" spans="3:4">
+      <c r="C32" s="18"/>
+      <c r="D32" s="22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="4:4">
-      <c r="D24" s="19" t="s">
+    <row r="33" hidden="1" spans="3:4">
+      <c r="C33" s="18"/>
+      <c r="D33" s="22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="3:3">
-      <c r="C25" s="16" t="s">
+    <row r="34" hidden="1" spans="3:4">
+      <c r="C34" s="18"/>
+      <c r="D34" s="22" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" ht="31" hidden="1" spans="4:4">
-      <c r="D26" s="19" t="s">
+    <row r="35" hidden="1" spans="3:4">
+      <c r="C35" s="18"/>
+      <c r="D35" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="4:4">
-      <c r="D27" s="19" t="s">
+    <row r="36" hidden="1" spans="3:4">
+      <c r="C36" s="18"/>
+      <c r="D36" s="22" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="3:3">
-      <c r="C28" s="16" t="s">
+    <row r="37" hidden="1" spans="3:4">
+      <c r="C37" s="18"/>
+      <c r="D37" s="22" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" ht="31" hidden="1" spans="4:4">
-      <c r="D29" s="19" t="s">
+    <row r="38" hidden="1" spans="3:4">
+      <c r="C38" s="18"/>
+      <c r="D38" s="22" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="4:4">
-      <c r="D30" s="19" t="s">
+    <row r="39" ht="31" hidden="1" spans="3:4">
+      <c r="C39" s="18"/>
+      <c r="D39" s="22" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="3:3">
-      <c r="C31" s="16" t="s">
+    <row r="40" hidden="1" spans="3:3">
+      <c r="C40" s="18"/>
+    </row>
+    <row r="41" hidden="1" spans="3:3">
+      <c r="C41" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="4:4">
-      <c r="D32" s="19" t="s">
+    <row r="42" ht="14" hidden="1" customHeight="1" spans="3:4">
+      <c r="C42" s="18"/>
+      <c r="D42" s="22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="4:4">
-      <c r="D33" s="19" t="s">
+    <row r="43" hidden="1" spans="3:4">
+      <c r="C43" s="18"/>
+      <c r="D43" s="22" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="3:3">
-      <c r="C34" s="16" t="s">
+    <row r="44" hidden="1" spans="3:4">
+      <c r="C44" s="18"/>
+      <c r="D44" s="22" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="4:4">
-      <c r="D35" s="19" t="s">
+    <row r="45" hidden="1" spans="3:4">
+      <c r="C45" s="18"/>
+      <c r="D45" s="22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="3:3">
-      <c r="C36" s="16" t="s">
+    <row r="46" hidden="1" spans="3:3">
+      <c r="C46" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" ht="31" hidden="1" spans="4:4">
-      <c r="D37" s="19" t="s">
+    <row r="47" ht="31" hidden="1" spans="3:4">
+      <c r="C47" s="18"/>
+      <c r="D47" s="22" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="4:4">
-      <c r="D38" s="19" t="s">
+    <row r="48" hidden="1" spans="3:4">
+      <c r="C48" s="18"/>
+      <c r="D48" s="22" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="3:3">
-      <c r="C39" s="16" t="s">
+    <row r="49" hidden="1" spans="3:3">
+      <c r="C49" s="18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" ht="46.5" hidden="1" spans="4:4">
-      <c r="D40" s="19" t="s">
+    <row r="50" ht="31" hidden="1" spans="3:4">
+      <c r="C50" s="18"/>
+      <c r="D50" s="22" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="4:4">
-      <c r="D41" s="19" t="s">
+    <row r="51" hidden="1" spans="3:4">
+      <c r="C51" s="18"/>
+      <c r="D51" s="22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="3:3">
+      <c r="C52" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="3:4">
+      <c r="C53" s="18"/>
+      <c r="D53" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" spans="3:4">
+      <c r="C54" s="18"/>
+      <c r="D54" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" spans="3:3">
+      <c r="C55" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" spans="3:4">
+      <c r="C56" s="18"/>
+      <c r="D56" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" spans="3:3">
+      <c r="C57" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" ht="31" hidden="1" spans="3:4">
+      <c r="C58" s="18"/>
+      <c r="D58" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" spans="3:4">
+      <c r="C59" s="18"/>
+      <c r="D59" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" spans="3:3">
+      <c r="C60" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" ht="46.5" hidden="1" spans="3:4">
+      <c r="C61" s="18"/>
+      <c r="D61" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" spans="3:4">
+      <c r="C62" s="18"/>
+      <c r="D62" s="22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="4:4">
-      <c r="D42" s="19" t="s">
+    <row r="63" hidden="1" spans="3:4">
+      <c r="C63" s="18"/>
+      <c r="D63" s="22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="3:3">
-      <c r="C43" s="16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" ht="14" hidden="1" customHeight="1" spans="4:4">
-      <c r="D44" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" hidden="1" spans="4:4">
-      <c r="D45" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" hidden="1" spans="4:4">
-      <c r="D46" s="19" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" hidden="1" spans="4:4">
-      <c r="D47" s="19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" hidden="1" spans="3:3">
-      <c r="C48" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" ht="46.5" hidden="1" spans="4:4">
-      <c r="D49" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" hidden="1" spans="4:4">
-      <c r="D50" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" hidden="1" spans="3:3">
-      <c r="C51" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" ht="31" hidden="1" spans="4:4">
-      <c r="D52" s="19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" hidden="1" spans="4:4">
-      <c r="D53" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" hidden="1" spans="4:4">
-      <c r="D54" s="19" t="s">
+    <row r="64" hidden="1" spans="3:3">
+      <c r="C64" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="15" t="s">
+    <row r="65" ht="46.5" hidden="1" spans="3:4">
+      <c r="C65" s="18"/>
+      <c r="D65" s="22" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="3:3">
-      <c r="C57" s="16" t="s">
+    <row r="66" hidden="1" spans="3:4">
+      <c r="C66" s="18"/>
+      <c r="D66" s="22" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="4:4">
-      <c r="D58" s="19" t="s">
+    <row r="67" hidden="1" spans="3:3">
+      <c r="C67" s="18" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="3:4">
-      <c r="C59" s="21"/>
-      <c r="D59" s="22" t="s">
+    <row r="68" ht="31" hidden="1" spans="3:4">
+      <c r="C68" s="18"/>
+      <c r="D68" s="22" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="31" hidden="1" spans="3:4">
-      <c r="C60" s="21" t="s">
+    <row r="69" hidden="1" spans="4:4">
+      <c r="D69" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D60" s="22" t="s">
+    </row>
+    <row r="70" hidden="1" spans="4:4">
+      <c r="D70" s="22" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="61" ht="31" hidden="1" spans="3:4">
-      <c r="C61" s="21" t="s">
+    <row r="72" spans="2:2">
+      <c r="B72" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="22" t="s">
+    </row>
+    <row r="73" spans="3:3">
+      <c r="C73" s="19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="3:4">
-      <c r="C62" s="21" t="s">
+    <row r="74" hidden="1" spans="4:4">
+      <c r="D74" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D62" s="22"/>
-    </row>
-    <row r="63" ht="31" hidden="1" spans="3:4">
-      <c r="C63" s="21"/>
-      <c r="D63" s="22" t="s">
+    </row>
+    <row r="75" hidden="1" spans="3:4">
+      <c r="C75" s="24"/>
+      <c r="D75" s="22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="3:4">
-      <c r="C64" s="21"/>
-      <c r="D64" s="22" t="s">
+    <row r="76" ht="31" hidden="1" spans="3:4">
+      <c r="C76" s="24" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="65" ht="33" hidden="1" customHeight="1" spans="3:4">
-      <c r="C65" s="21"/>
-      <c r="D65" s="22" t="s">
+      <c r="D76" s="22" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="3:4">
-      <c r="C66" s="21" t="s">
+    <row r="77" ht="31" hidden="1" spans="3:4">
+      <c r="C77" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="22"/>
-    </row>
-    <row r="67" hidden="1" spans="3:4">
-      <c r="C67" s="21"/>
-      <c r="D67" s="22" t="s">
+      <c r="D77" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="68" ht="31" hidden="1" spans="3:4">
-      <c r="C68" s="21"/>
-      <c r="D68" s="22" t="s">
+    <row r="78" hidden="1" spans="3:3">
+      <c r="C78" s="24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="69" ht="46.5" hidden="1" spans="3:4">
-      <c r="C69" s="21"/>
-      <c r="D69" s="22" t="s">
+    <row r="79" ht="31" hidden="1" spans="3:4">
+      <c r="C79" s="24"/>
+      <c r="D79" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="3:4">
-      <c r="C70" s="21" t="s">
+    <row r="80" hidden="1" spans="3:4">
+      <c r="C80" s="24"/>
+      <c r="D80" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="22"/>
-    </row>
-    <row r="71" ht="31" hidden="1" spans="3:4">
-      <c r="C71" s="21"/>
-      <c r="D71" s="22" t="s">
+    </row>
+    <row r="81" ht="33" hidden="1" customHeight="1" spans="3:4">
+      <c r="C81" s="24"/>
+      <c r="D81" s="22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="3:4">
-      <c r="C72" s="21"/>
-      <c r="D72" s="22" t="s">
+    <row r="82" hidden="1" spans="3:3">
+      <c r="C82" s="24" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="3:4">
-      <c r="C73" s="21"/>
-      <c r="D73" s="22" t="s">
+    <row r="83" hidden="1" spans="3:4">
+      <c r="C83" s="24"/>
+      <c r="D83" s="22" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="3:4">
-      <c r="C74" s="21"/>
-      <c r="D74" s="22" t="s">
+    <row r="84" ht="31" hidden="1" spans="3:4">
+      <c r="C84" s="24"/>
+      <c r="D84" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="3:4">
-      <c r="C75" s="21"/>
-      <c r="D75" s="22" t="s">
+    <row r="85" ht="46.5" hidden="1" spans="3:4">
+      <c r="C85" s="24"/>
+      <c r="D85" s="22" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="3:4">
-      <c r="C76" s="21"/>
-      <c r="D76" s="22" t="s">
+    <row r="86" hidden="1" spans="3:3">
+      <c r="C86" s="24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="3:4">
-      <c r="C77" s="21"/>
-      <c r="D77" s="22" t="s">
+    <row r="87" ht="31" hidden="1" spans="3:4">
+      <c r="C87" s="24"/>
+      <c r="D87" s="22" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="3:4">
-      <c r="C78" s="21" t="s">
+    <row r="88" hidden="1" spans="3:4">
+      <c r="C88" s="24"/>
+      <c r="D88" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="22"/>
-    </row>
-    <row r="79" ht="31" hidden="1" spans="3:4">
-      <c r="C79" s="21"/>
-      <c r="D79" s="22" t="s">
+    </row>
+    <row r="89" hidden="1" spans="3:4">
+      <c r="C89" s="24"/>
+      <c r="D89" s="22" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="4:4">
-      <c r="D80" s="19" t="s">
+    <row r="90" hidden="1" spans="3:4">
+      <c r="C90" s="24"/>
+      <c r="D90" s="22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="81" ht="31" hidden="1" spans="4:4">
-      <c r="D81" s="19" t="s">
+    <row r="91" hidden="1" spans="3:4">
+      <c r="C91" s="24"/>
+      <c r="D91" s="22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="3:3">
-      <c r="C82" s="16" t="s">
+    <row r="92" hidden="1" spans="3:4">
+      <c r="C92" s="24"/>
+      <c r="D92" s="22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="83" ht="31" hidden="1" spans="4:4">
-      <c r="D83" s="19" t="s">
+    <row r="93" hidden="1" spans="3:4">
+      <c r="C93" s="24"/>
+      <c r="D93" s="22" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="15" t="s">
+    <row r="94" hidden="1" spans="3:3">
+      <c r="C94" s="24" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="4:4">
-      <c r="D86" s="19" t="s">
+    <row r="95" ht="31" hidden="1" spans="3:4">
+      <c r="C95" s="24"/>
+      <c r="D95" s="22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="3:3">
-      <c r="C87" s="16" t="s">
+    <row r="96" hidden="1" spans="4:4">
+      <c r="D96" s="22" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="88" ht="31" hidden="1" spans="4:4">
-      <c r="D88" s="19" t="s">
+    <row r="97" ht="31" hidden="1" spans="4:4">
+      <c r="D97" s="22" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="3:3">
-      <c r="C89" s="16" t="s">
+    <row r="98" hidden="1" spans="3:3">
+      <c r="C98" s="19" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="90" ht="31" hidden="1" spans="4:4">
-      <c r="D90" s="19" t="s">
+    <row r="99" ht="31" hidden="1" spans="4:4">
+      <c r="D99" s="22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="4:4">
-      <c r="D91" s="19" t="s">
+    <row r="101" spans="2:2">
+      <c r="B101" s="18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="3:3">
-      <c r="C92" s="16" t="s">
+    <row r="102" spans="4:4">
+      <c r="D102" s="22" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="93" ht="31" hidden="1" spans="4:4">
-      <c r="D93" s="19" t="s">
+    <row r="103" hidden="1" spans="3:3">
+      <c r="C103" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="4:4">
-      <c r="D94" s="19" t="s">
+    <row r="104" ht="31" hidden="1" spans="4:4">
+      <c r="D104" s="22" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="3:3">
-      <c r="C95" s="16" t="s">
+    <row r="105" hidden="1" spans="3:3">
+      <c r="C105" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="96" ht="31" hidden="1" spans="4:4">
-      <c r="D96" s="19" t="s">
+    <row r="106" ht="31" hidden="1" spans="4:4">
+      <c r="D106" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="4:4">
-      <c r="D97" s="19" t="s">
+    <row r="107" hidden="1" spans="4:4">
+      <c r="D107" s="22" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="15" t="s">
+    <row r="108" hidden="1" spans="3:3">
+      <c r="C108" s="19" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="100" ht="31" spans="4:4">
-      <c r="D100" s="19" t="s">
+    <row r="109" ht="31" hidden="1" spans="4:4">
+      <c r="D109" s="22" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="3:3">
-      <c r="C101" s="16" t="s">
+    <row r="110" hidden="1" spans="4:4">
+      <c r="D110" s="22" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="102" ht="31" hidden="1" spans="4:4">
-      <c r="D102" s="19" t="s">
+    <row r="111" hidden="1" spans="3:3">
+      <c r="C111" s="19" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="4:4">
-      <c r="D103" s="19" t="s">
+    <row r="112" ht="31" hidden="1" spans="4:4">
+      <c r="D112" s="22" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="3:3">
-      <c r="C104" s="16" t="s">
+    <row r="113" hidden="1" spans="4:4">
+      <c r="D113" s="22" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="105" ht="62" hidden="1" spans="4:4">
-      <c r="D105" s="19" t="s">
+    <row r="115" spans="2:2">
+      <c r="B115" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="4:4">
-      <c r="D106" s="19" t="s">
+    <row r="116" ht="31" spans="4:4">
+      <c r="D116" s="22" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="3:3">
-      <c r="C107" s="16" t="s">
+    <row r="117" hidden="1" spans="3:3">
+      <c r="C117" s="19" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="4:4">
-      <c r="D108" s="19" t="s">
+    <row r="118" ht="31" hidden="1" spans="4:4">
+      <c r="D118" s="22" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="4:4">
-      <c r="D109" s="19" t="s">
+    <row r="119" hidden="1" spans="4:4">
+      <c r="D119" s="22" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="4:4">
-      <c r="D110" s="19" t="s">
+    <row r="120" hidden="1" spans="3:3">
+      <c r="C120" s="19" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="4:4">
-      <c r="D111" s="19" t="s">
+    <row r="121" ht="62" hidden="1" spans="4:4">
+      <c r="D121" s="22" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="112" ht="31" hidden="1" spans="4:4">
-      <c r="D112" s="23" t="s">
+    <row r="122" hidden="1" spans="4:4">
+      <c r="D122" s="22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="4:4">
-      <c r="D113" s="23" t="s">
+    <row r="123" hidden="1" spans="3:3">
+      <c r="C123" s="19" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="4:4">
-      <c r="D114" s="23" t="s">
+    <row r="124" hidden="1" spans="4:4">
+      <c r="D124" s="22" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="4:4">
-      <c r="D115" s="23" t="s">
+    <row r="125" hidden="1" spans="4:4">
+      <c r="D125" s="22" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="4:4">
-      <c r="D116" s="23" t="s">
+    <row r="126" hidden="1" spans="4:4">
+      <c r="D126" s="22" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="3:3">
-      <c r="C117" s="16" t="s">
+    <row r="127" hidden="1" spans="4:4">
+      <c r="D127" s="22" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="118" ht="31" hidden="1" spans="4:4">
-      <c r="D118" s="19" t="s">
+    <row r="128" ht="31" hidden="1" spans="4:4">
+      <c r="D128" s="25" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="4:4">
-      <c r="D119" s="19" t="s">
+    <row r="129" hidden="1" spans="4:4">
+      <c r="D129" s="25" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="120" ht="31" hidden="1" spans="4:4">
-      <c r="D120" s="19" t="s">
+    <row r="130" hidden="1" spans="4:4">
+      <c r="D130" s="25" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="3:3">
-      <c r="C121" s="16" t="s">
+    <row r="131" hidden="1" spans="4:4">
+      <c r="D131" s="25" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="4:4">
-      <c r="D122" s="19" t="s">
+    <row r="132" hidden="1" spans="4:4">
+      <c r="D132" s="25" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="123" ht="31" hidden="1" spans="4:4">
-      <c r="D123" s="19" t="s">
+    <row r="133" hidden="1" spans="3:3">
+      <c r="C133" s="19" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="4:4">
-      <c r="D124" s="19" t="s">
+    <row r="134" ht="31" hidden="1" spans="4:4">
+      <c r="D134" s="22" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="4:4">
-      <c r="D125" s="19" t="s">
+    <row r="135" hidden="1" spans="4:4">
+      <c r="D135" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="4:4">
-      <c r="D126" s="19" t="s">
+    <row r="136" ht="31" hidden="1" spans="4:4">
+      <c r="D136" s="22" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="4:4">
-      <c r="D127" s="19" t="s">
+    <row r="137" hidden="1" spans="3:3">
+      <c r="C137" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="128" ht="31" hidden="1" spans="4:4">
-      <c r="D128" s="19" t="s">
+    <row r="138" hidden="1" spans="4:4">
+      <c r="D138" s="22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="3:3">
-      <c r="C129" s="16" t="s">
+    <row r="139" ht="31" hidden="1" spans="4:4">
+      <c r="D139" s="22" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="130" ht="31" hidden="1" spans="4:4">
-      <c r="D130" s="19" t="s">
+    <row r="140" hidden="1" spans="4:4">
+      <c r="D140" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="4:4">
-      <c r="D131" s="19" t="s">
+    <row r="141" hidden="1" spans="4:4">
+      <c r="D141" s="22" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="3:3">
-      <c r="C132" s="16" t="s">
+    <row r="142" hidden="1" spans="4:4">
+      <c r="D142" s="22" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="133" ht="46.5" hidden="1" spans="4:4">
-      <c r="D133" s="19" t="s">
+    <row r="143" hidden="1" spans="4:4">
+      <c r="D143" s="22" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="4:4">
-      <c r="D134" s="19" t="s">
+    <row r="144" ht="31" hidden="1" spans="4:4">
+      <c r="D144" s="22" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="15" t="s">
+    <row r="145" hidden="1" spans="3:3">
+      <c r="C145" s="19" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="137" ht="31" spans="4:4">
-      <c r="D137" s="19" t="s">
+    <row r="146" ht="31" hidden="1" spans="4:4">
+      <c r="D146" s="22" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="4:4">
-      <c r="D138" s="19" t="s">
+    <row r="147" hidden="1" spans="4:4">
+      <c r="D147" s="22" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="3:3">
-      <c r="C139" s="16" t="s">
+    <row r="148" hidden="1" spans="3:3">
+      <c r="C148" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="140" ht="31" hidden="1" spans="4:4">
-      <c r="D140" s="19" t="s">
+    <row r="149" ht="46.5" hidden="1" spans="4:4">
+      <c r="D149" s="22" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="4:4">
-      <c r="D141" s="19" t="s">
+    <row r="150" hidden="1" spans="4:4">
+      <c r="D150" s="22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="3:3">
-      <c r="C142" s="16" t="s">
+    <row r="152" spans="2:2">
+      <c r="B152" s="18" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="143" ht="31" hidden="1" spans="4:4">
-      <c r="D143" s="19" t="s">
+    <row r="153" ht="31" spans="4:4">
+      <c r="D153" s="22" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="4:4">
-      <c r="D144" s="19" t="s">
+    <row r="154" spans="4:4">
+      <c r="D154" s="22" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="3:3">
-      <c r="C145" s="16" t="s">
+    <row r="155" hidden="1" spans="3:3">
+      <c r="C155" s="19" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="4:4">
-      <c r="D146" s="19" t="s">
+    <row r="156" ht="31" hidden="1" spans="4:4">
+      <c r="D156" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="4:4">
-      <c r="D147" s="19" t="s">
+    <row r="157" hidden="1" spans="4:4">
+      <c r="D157" s="22" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="3:3">
-      <c r="C148" s="16" t="s">
+    <row r="158" hidden="1" spans="3:3">
+      <c r="C158" s="19" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="149" ht="31" hidden="1" spans="4:4">
-      <c r="D149" s="19" t="s">
+    <row r="159" ht="31" hidden="1" spans="4:4">
+      <c r="D159" s="22" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="4:4">
-      <c r="D150" s="19" t="s">
+    <row r="160" hidden="1" spans="4:4">
+      <c r="D160" s="22" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="4:4">
-      <c r="D151" s="19" t="s">
+    <row r="161" hidden="1" spans="3:3">
+      <c r="C161" s="19" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="24" t="s">
+    <row r="162" hidden="1" spans="4:4">
+      <c r="D162" s="22" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="16" t="s">
+    <row r="163" hidden="1" spans="4:4">
+      <c r="D163" s="22" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="16" t="s">
+    <row r="164" hidden="1" spans="3:3">
+      <c r="C164" s="19" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="15" t="s">
+    <row r="165" ht="31" hidden="1" spans="4:4">
+      <c r="D165" s="22" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="157" spans="3:3">
-      <c r="C157" s="16" t="s">
+    <row r="166" hidden="1" spans="4:4">
+      <c r="D166" s="22" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="158" spans="3:3">
-      <c r="C158" s="16" t="s">
+    <row r="167" hidden="1" spans="4:4">
+      <c r="D167" s="22" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="159" spans="3:3">
-      <c r="C159" s="16" t="s">
+    <row r="169" spans="1:1">
+      <c r="A169" s="26" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="160" spans="3:3">
-      <c r="C160" s="16" t="s">
+    <row r="170" spans="1:1">
+      <c r="A170" s="19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="161" spans="3:3">
-      <c r="C161" s="16" t="s">
+    <row r="171" spans="2:2">
+      <c r="B171" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="162" ht="31" spans="4:4">
-      <c r="D162" s="19" t="s">
+    <row r="172" spans="2:2">
+      <c r="B172" s="18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="163" spans="3:3">
-      <c r="C163" s="16" t="s">
+    <row r="173" hidden="1" spans="3:3">
+      <c r="C173" s="19" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="165" spans="3:3">
-      <c r="C165" s="16" t="s">
+    <row r="174" hidden="1" spans="3:3">
+      <c r="C174" s="19" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="166" spans="3:3">
-      <c r="C166" s="16" t="s">
+    <row r="175" hidden="1" spans="3:3">
+      <c r="C175" s="19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="167" spans="3:3">
-      <c r="C167" s="16" t="s">
+    <row r="176" hidden="1" spans="3:3">
+      <c r="C176" s="19" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="168" spans="4:4">
-      <c r="D168" s="19" t="s">
+    <row r="177" hidden="1" spans="3:3">
+      <c r="C177" s="19" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="170" spans="3:3">
-      <c r="C170" s="16" t="s">
+    <row r="178" ht="31" hidden="1" spans="4:4">
+      <c r="D178" s="22" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="15"/>
-      <c r="B172" s="15" t="s">
+    <row r="179" hidden="1" spans="3:3">
+      <c r="C179" s="19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
-      <c r="A173" s="15"/>
-      <c r="B173" s="15"/>
-      <c r="C173" s="16" t="s">
+    <row r="180" hidden="1"/>
+    <row r="181" hidden="1" spans="3:3">
+      <c r="C181" s="19" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="15"/>
-      <c r="B174" s="15"/>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="15"/>
-      <c r="B175" s="15" t="s">
+    <row r="182" hidden="1" spans="3:3">
+      <c r="C182" s="19" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
-      <c r="A176" s="15"/>
-      <c r="B176" s="15"/>
-      <c r="C176" s="16" t="s">
+    <row r="183" hidden="1" spans="3:3">
+      <c r="C183" s="19" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="184" hidden="1" spans="4:4">
+      <c r="D184" s="22" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="185" hidden="1"/>
+    <row r="186" hidden="1" spans="3:3">
+      <c r="C186" s="19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="18"/>
+      <c r="B188" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="18"/>
+      <c r="B189" s="18"/>
+      <c r="C189" s="19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="18"/>
+      <c r="B190" s="18"/>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="18"/>
+      <c r="B191" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="18"/>
+      <c r="B192" s="18"/>
+      <c r="C192" s="19" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4661,385 +5150,385 @@
   <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="4" style="9" customWidth="1"/>
-    <col min="4" max="4" width="130.461538461538" style="10" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="9"/>
+    <col min="1" max="3" width="4" style="10" customWidth="1"/>
+    <col min="4" max="4" width="130.461538461538" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="A1" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16" t="s">
-        <v>232</v>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16" t="s">
-        <v>233</v>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="16"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" spans="2:3">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="21" spans="3:3">
-      <c r="C21" s="9" t="s">
-        <v>235</v>
+      <c r="C21" s="10" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="4:4">
-      <c r="D22" s="10" t="s">
-        <v>236</v>
+      <c r="D22" s="11" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="10" t="s">
-        <v>237</v>
+      <c r="D23" s="11" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="3:3">
-      <c r="C25" s="9" t="s">
-        <v>238</v>
+      <c r="C25" s="10" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="4:4">
-      <c r="D26" s="10" t="s">
-        <v>115</v>
+      <c r="D26" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="4:4">
-      <c r="D27" s="10" t="s">
-        <v>239</v>
+      <c r="D27" s="11" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" s="17" t="s">
-        <v>240</v>
+      <c r="B29" s="20" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="4:4">
-      <c r="D30" s="10" t="s">
-        <v>241</v>
+      <c r="D30" s="11" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="31" ht="31" spans="4:4">
-      <c r="D31" s="10" t="s">
-        <v>242</v>
+      <c r="D31" s="11" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="4:4">
-      <c r="D32" s="18" t="s">
-        <v>243</v>
+      <c r="D32" s="21" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="4:4">
-      <c r="D33" s="18" t="s">
-        <v>244</v>
+      <c r="D33" s="21" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="4:4">
-      <c r="D34" s="18" t="s">
-        <v>245</v>
+      <c r="D34" s="21" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="4:4">
-      <c r="D35" s="18" t="s">
-        <v>246</v>
+      <c r="D35" s="21" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="36" ht="31" spans="4:4">
-      <c r="D36" s="10" t="s">
-        <v>247</v>
+      <c r="D36" s="11" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="17" t="s">
-        <v>248</v>
+      <c r="B38" s="20" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="17"/>
-      <c r="D39" s="10" t="s">
+      <c r="B39" s="20"/>
+      <c r="D39" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="40" ht="31" spans="4:4">
-      <c r="D40" s="10" t="s">
-        <v>249</v>
+      <c r="D40" s="11" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="42" ht="31" spans="4:4">
-      <c r="D42" s="10" t="s">
-        <v>250</v>
+      <c r="D42" s="11" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>254</v>
+      <c r="A43" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>258</v>
+      <c r="A44" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>261</v>
+      <c r="A45" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="2:4">
-      <c r="B46" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>264</v>
+      <c r="B46" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="2:4">
-      <c r="B47" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>267</v>
+      <c r="B47" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="4:4">
-      <c r="D48" s="9" t="s">
-        <v>268</v>
+      <c r="D48" s="10" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="2:2">
-      <c r="B50" s="17" t="s">
-        <v>269</v>
+      <c r="B50" s="20" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="51" ht="46.5" spans="4:4">
-      <c r="D51" s="10" t="s">
-        <v>270</v>
+      <c r="D51" s="11" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="4:4">
-      <c r="D53" s="10" t="s">
-        <v>271</v>
+      <c r="D53" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="54" ht="62" spans="4:4">
-      <c r="D54" s="10" t="s">
-        <v>272</v>
+      <c r="D54" s="11" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="10" t="s">
-        <v>273</v>
+      <c r="D56" s="21" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="57" ht="46.5" spans="4:4">
-      <c r="D57" s="10" t="s">
-        <v>274</v>
+      <c r="D57" s="11" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="59" ht="31" spans="4:4">
-      <c r="D59" s="10" t="s">
-        <v>275</v>
+      <c r="D59" s="11" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="60" spans="4:4">
-      <c r="D60" s="10" t="s">
-        <v>276</v>
+      <c r="D60" s="11" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="2:2">
-      <c r="B62" s="17" t="s">
-        <v>277</v>
+      <c r="B62" s="20" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="63" spans="2:3">
-      <c r="B63" s="17"/>
-      <c r="C63" s="9" t="s">
-        <v>278</v>
+      <c r="B63" s="20"/>
+      <c r="C63" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="64" ht="46.5" spans="2:4">
-      <c r="B64" s="17"/>
-      <c r="D64" s="10" t="s">
-        <v>279</v>
+      <c r="B64" s="20"/>
+      <c r="D64" s="11" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="2:4">
-      <c r="B65" s="17"/>
-      <c r="D65" s="10" t="s">
-        <v>280</v>
+      <c r="B65" s="20"/>
+      <c r="D65" s="11" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="2:4">
-      <c r="B66" s="17"/>
-      <c r="D66" s="10" t="s">
-        <v>281</v>
+      <c r="B66" s="20"/>
+      <c r="D66" s="11" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="2:4">
-      <c r="B67" s="17"/>
-      <c r="D67" s="10" t="s">
-        <v>111</v>
+      <c r="B67" s="20"/>
+      <c r="D67" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="2:4">
-      <c r="B68" s="17"/>
-      <c r="D68" s="10" t="s">
-        <v>282</v>
+      <c r="B68" s="20"/>
+      <c r="D68" s="11" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="17"/>
+      <c r="B69" s="20"/>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="17" t="s">
-        <v>283</v>
+      <c r="B70" s="20" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="3:3">
-      <c r="C71" s="9" t="s">
-        <v>284</v>
+      <c r="C71" s="10" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="4:4">
-      <c r="D72" s="18" t="s">
-        <v>285</v>
+      <c r="D72" s="21" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="4:4">
-      <c r="D73" s="10" t="s">
-        <v>286</v>
+      <c r="D73" s="11" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="4:4">
-      <c r="D74" s="10" t="s">
-        <v>287</v>
+      <c r="D74" s="11" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="4:4">
-      <c r="D75" s="10" t="s">
-        <v>288</v>
+      <c r="D75" s="11" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="4:4">
-      <c r="D77" s="18" t="s">
-        <v>289</v>
+      <c r="D77" s="21" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="4:4">
-      <c r="D78" s="10" t="s">
-        <v>290</v>
+      <c r="D78" s="11" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="79" ht="31" spans="4:4">
-      <c r="D79" s="10" t="s">
-        <v>291</v>
+      <c r="D79" s="11" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="4:4">
-      <c r="D81" s="10" t="s">
-        <v>292</v>
+      <c r="D81" s="11" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="4:4">
-      <c r="D82" s="10" t="s">
-        <v>293</v>
+      <c r="D82" s="11" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="10" t="s">
-        <v>294</v>
+      <c r="D83" s="11" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="4:4">
-      <c r="D85" s="10" t="s">
-        <v>295</v>
+      <c r="D85" s="11" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="10" t="s">
-        <v>296</v>
+      <c r="D86" s="11" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="87" ht="31" spans="4:4">
-      <c r="D87" s="10" t="s">
-        <v>297</v>
+      <c r="D87" s="11" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5052,184 +5541,303 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="3" style="11" customWidth="1"/>
-    <col min="4" max="4" width="156.923076923077" style="12" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="11"/>
+    <col min="1" max="3" width="3" style="13" customWidth="1"/>
+    <col min="4" max="4" width="156.923076923077" style="14" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
-        <v>298</v>
+      <c r="A1" s="15" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="4:4">
-      <c r="D2" s="12" t="s">
-        <v>299</v>
+      <c r="D2" s="14" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="46.5" spans="4:4">
-      <c r="D3" s="12" t="s">
-        <v>300</v>
+      <c r="D3" s="14" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
-        <v>301</v>
+      <c r="A4" s="15" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="13" t="s">
-        <v>302</v>
+      <c r="B5" s="15" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="11" t="s">
-        <v>303</v>
+      <c r="C6" s="13" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="13" t="s">
-        <v>304</v>
+      <c r="C7" s="15" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="8" ht="31" spans="3:4">
-      <c r="C8" s="13"/>
-      <c r="D8" s="12" t="s">
-        <v>305</v>
+      <c r="C8" s="15"/>
+      <c r="D8" s="14" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="9" ht="93" spans="3:4">
-      <c r="C9" s="13"/>
-      <c r="D9" s="14" t="s">
-        <v>306</v>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="77.5" spans="3:4">
-      <c r="C10" s="13"/>
-      <c r="D10" s="14" t="s">
-        <v>307</v>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="3:3">
-      <c r="C11" s="13"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="3:3">
-      <c r="C12" s="13" t="s">
-        <v>308</v>
+      <c r="C12" s="15" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="13" ht="31" spans="3:4">
-      <c r="C13" s="13"/>
-      <c r="D13" s="12" t="s">
-        <v>309</v>
+      <c r="C13" s="15"/>
+      <c r="D13" s="14" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="14" ht="93" spans="4:4">
-      <c r="D14" s="14" t="s">
-        <v>310</v>
+      <c r="D14" s="16" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="15" ht="77.5" spans="4:4">
-      <c r="D15" s="14" t="s">
-        <v>311</v>
+      <c r="D15" s="16" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="17" ht="46.5" spans="4:4">
-      <c r="D17" s="14" t="s">
-        <v>312</v>
+      <c r="D17" s="16" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="3:3">
-      <c r="C19" s="13" t="s">
-        <v>313</v>
+      <c r="C19" s="15" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="4:4">
-      <c r="D20" s="12" t="s">
-        <v>314</v>
+      <c r="D20" s="14" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="3:3">
-      <c r="C22" s="13" t="s">
-        <v>315</v>
+      <c r="C22" s="15" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="12" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="B230" s="13"/>
-      <c r="C230" s="13"/>
-      <c r="D230" s="14" t="s">
-        <v>318</v>
+      <c r="D23" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="D26" s="14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="D29" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="D32" s="14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="D35" s="14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="D38" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" s="17" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4">
+      <c r="C44" s="17"/>
+      <c r="D44" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="45" ht="93" spans="4:4">
+      <c r="D45" s="14" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D231" s="12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="232" ht="31" spans="1:4">
-      <c r="A232" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="B232" s="12"/>
-      <c r="C232" s="12"/>
-      <c r="D232" s="12" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="233" ht="46.5" spans="1:4">
-      <c r="A233" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="B233" s="12"/>
-      <c r="C233" s="12"/>
-      <c r="D233" s="12" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4">
-      <c r="A235" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="B235" s="13"/>
-      <c r="C235" s="13"/>
-      <c r="D235" s="14" t="s">
-        <v>318</v>
+      <c r="A231" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B231" s="15"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="16" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D232" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="233" ht="31" spans="1:4">
+      <c r="A233" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B233" s="14"/>
+      <c r="C233" s="14"/>
+      <c r="D233" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="234" ht="46.5" spans="1:4">
+      <c r="A234" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B234" s="14"/>
+      <c r="C234" s="14"/>
+      <c r="D234" s="14" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="D236" s="12" t="s">
-        <v>327</v>
+      <c r="A236" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B236" s="15"/>
+      <c r="C236" s="15"/>
+      <c r="D236" s="16" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="D237" s="12" t="s">
-        <v>329</v>
+      <c r="A237" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D238" s="14" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A232:C232"/>
     <mergeCell ref="A233:C233"/>
+    <mergeCell ref="A234:C234"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5245,7 +5853,7 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5257,9 +5865,71 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
-  <sheetData/>
+  <dimension ref="A5:E26"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="3" width="1.84615384615385" customWidth="1"/>
+    <col min="4" max="4" width="2.07692307692308" customWidth="1"/>
+    <col min="5" max="5" width="156.769230769231" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" ht="201.5" spans="1:5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" ht="93" spans="5:5">
+      <c r="E10" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5282,56 +5952,56 @@
   <dimension ref="B1:D15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="2.76923076923077" style="9" customWidth="1"/>
-    <col min="2" max="2" width="2.61538461538462" style="9" customWidth="1"/>
-    <col min="3" max="3" width="3.23076923076923" style="9" customWidth="1"/>
-    <col min="4" max="4" width="153.615384615385" style="10" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="9"/>
+    <col min="1" max="1" width="2.76923076923077" style="10" customWidth="1"/>
+    <col min="2" max="2" width="2.61538461538462" style="10" customWidth="1"/>
+    <col min="3" max="3" width="3.23076923076923" style="10" customWidth="1"/>
+    <col min="4" max="4" width="153.615384615385" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="9" t="s">
-        <v>331</v>
+      <c r="B1" s="10" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="3:3">
-      <c r="C2" s="9" t="s">
-        <v>332</v>
+      <c r="C2" s="10" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="5" ht="31" spans="4:4">
-      <c r="D5" s="10" t="s">
-        <v>333</v>
+      <c r="D5" s="11" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="7" ht="31" spans="4:4">
-      <c r="D7" s="10" t="s">
-        <v>334</v>
+      <c r="D7" s="11" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="9" ht="31" spans="4:4">
-      <c r="D9" s="10" t="s">
-        <v>335</v>
+      <c r="D9" s="11" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="10" t="s">
-        <v>336</v>
+      <c r="D11" s="11" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="13" ht="31" spans="4:4">
-      <c r="D13" s="10" t="s">
-        <v>337</v>
+      <c r="D13" s="11" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" spans="4:4">
-      <c r="D14" s="10" t="s">
-        <v>338</v>
+      <c r="D14" s="11" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="4:4">
-      <c r="D15" s="10" t="s">
-        <v>339</v>
+      <c r="D15" s="11" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/p/ds_25/databricks/topic-list_DtBrk.xlsx
+++ b/p/ds_25/databricks/topic-list_DtBrk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="698" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="698" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="what-how" sheetId="21" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="OLTP" sheetId="31" r:id="rId8"/>
     <sheet name="ML" sheetId="30" r:id="rId9"/>
     <sheet name="core" sheetId="2" r:id="rId10"/>
-    <sheet name="walk" sheetId="33" r:id="rId11"/>
+    <sheet name="steps" sheetId="33" r:id="rId11"/>
+    <sheet name="log" sheetId="34" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4207,6 +4208,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
